--- a/📊 StudyTools_Websites_Master_List.xlsx
+++ b/📊 StudyTools_Websites_Master_List.xlsx
@@ -470,14 +470,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -494,17 +494,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Official Website URL</t>
+          <t>Exact Official Website URL</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Key Function / Description</t>
+          <t>Key Function / Purpose (StudyTools)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Source Video Title</t>
+          <t>Source Video Title (StudyTools)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -521,27 +521,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>3 Work From Home Jobs Websites</t>
+          <t>1 crore ka stipend</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Work+From+Home+Jobs+Websites</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Work From Home Jobs Websites</t>
+          <t>Online productivity web tool featured in StudyTools: 1 Crore ka Stipend</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>3 Work From Home Jobs Websites</t>
+          <t>1 Crore ka Stipend</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/yK6D7ltlTe4</t>
+          <t>https://www.youtube.com/shorts/UtRHDDOAGjM</t>
         </is>
       </c>
     </row>
@@ -553,27 +553,27 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Notion / StudySmarter</t>
+          <t>12th ke baad ?</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>https://notion.so</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Smart workspace to organize notes, flashcards, study schedules, and project tasks.</t>
+          <t>Online productivity web tool featured in StudyTools: 12th Ke Baad ?</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Learn any Topic in 5 Minutes</t>
+          <t>12th Ke Baad ?</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/CVX6Gex7YB8</t>
+          <t>https://www.youtube.com/shorts/uMsFNowAu-Q</t>
         </is>
       </c>
     </row>
@@ -585,667 +585,667 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TypeRacer / Keybr</t>
+          <t>2 best career options after 12th</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>https://play.typeracer.com</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Multiplayer typing speed test and keyboard touch-typing practice web app.</t>
+          <t>Online productivity web tool featured in StudyTools: 2 Best Career Options after 12th</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3 Best Websites for Learning Typing</t>
+          <t>2 Best Career Options after 12th</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/l2LyfnX-zUE</t>
+          <t>https://www.youtube.com/shorts/hJ9PFgjdg3Y</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>🎨 Design, 3D &amp; Graphics</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Arts Students</t>
+          <t>2 secret ai tools omg !</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Websites+for+Arts+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Websites for Arts Students</t>
+          <t>Online productivity web tool featured in StudyTools: 2 Secret AI tools OMG !</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Arts Students</t>
+          <t>2 Secret AI tools OMG !</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/IYtWNLqkeLg</t>
+          <t>https://www.youtube.com/shorts/XLkUpymwgdU</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🎨 Design, 3D &amp; Graphics</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Best Career Options for Arts Students</t>
+          <t>3 job platforms for freshers</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Career+Options+for+Arts+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Career Options for Arts Students</t>
+          <t>Online productivity web tool featured in StudyTools: 3 Job Platforms for Freshers</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Best Career Options for Arts Students</t>
+          <t>3 Job Platforms for Freshers</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/YDjuHSNftpk</t>
+          <t>https://www.youtube.com/shorts/-bXAtLlnv_s</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>03 Secret Websites for Students</t>
+          <t>3 work from home jobs websites</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=03+Secret+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 03 Secret Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: 3 Work From Home Jobs Websites</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>03 Secret Websites for Students</t>
+          <t>3 Work From Home Jobs Websites</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/c8s9y9ihRgM</t>
+          <t>https://www.youtube.com/shorts/yK6D7ltlTe4</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>03 Useful Websites for Students</t>
+          <t>4 high demand skills</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=03+Useful+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 03 Useful Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: 4 High Demand Skills</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>03 Useful Websites for Students</t>
+          <t>4 High Demand Skills</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/QqOuf147caI</t>
+          <t>https://www.youtube.com/shorts/BZap4r6NysM</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>10 Useful Websites for Students</t>
+          <t>5 skills that can make you rich</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=10+Useful+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 10 Useful Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: 5 Skills That Can Make You Rich</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>10 Useful Websites for Students</t>
+          <t>5 Skills That Can Make You Rich</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/IGsXbv52QC8</t>
+          <t>https://www.youtube.com/shorts/35FQ4kAmhEI</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2 Biggest Secrets for Students</t>
+          <t>6 top rated skills</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Biggest+Secrets+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Biggest Secrets for Students</t>
+          <t>Online productivity web tool featured in StudyTools: 6 Top Rated Skills</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2 Biggest Secrets for Students</t>
+          <t>6 Top Rated Skills</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/rt8mLZCbKFc</t>
+          <t>https://www.youtube.com/shorts/WYpv6tetXog</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2 Secret &amp; Useful Websites for Students</t>
+          <t>Ai skills for future growth</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret++Useful+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret &amp; Useful Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Learn AI Skills for Future Growth</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2 Secret &amp; Useful Websites for Students</t>
+          <t>Learn AI Skills for Future Growth</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/JidBL5RZUmg</t>
+          <t>w1uSgT_AJ9E</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2 Secret Websites for Students</t>
+          <t>Best internship after 12th</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Best Internship after 12th</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2 Secret Websites for Students</t>
+          <t>Best Internship after 12th</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Gwv-YREwC7A</t>
+          <t>https://www.youtube.com/shorts/OXk_XhJf_3s</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2 Useful Websites for Students</t>
+          <t>Best presentation maker ai tool</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Useful+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Useful Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Best Presentation Maker Ai tool</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2 Useful Websites for Students</t>
+          <t>Best Presentation Maker Ai tool</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/cPEdOw3187o</t>
+          <t>https://www.youtube.com/shorts/YS3WM7wjfrU</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2 Websites for Students</t>
+          <t>Ego into power</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Turn EGO into Power</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2 Websites for Students</t>
+          <t>Turn EGO into Power</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/jv0UexkG36A</t>
+          <t>https://www.youtube.com/shorts/uOKnC0dxgzI</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3 Amazing Websites for Students</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Amazing+Websites+for+Students</t>
+          <t>https://fi.money</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Amazing Websites for Students</t>
+          <t>Digital zero-balance banking and smart money management app for students.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>3 Amazing Websites for Students</t>
+          <t>4 Zero Balance Bank Accounts</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/1X4eiFCwD7s</t>
+          <t>https://www.youtube.com/shorts/8BF0ibAsGTU</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>3 Best Websites for Students</t>
+          <t>Free mock test</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Best+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Best Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Free Mock Test</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3 Best Websites for Students</t>
+          <t>Free Mock Test</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ABWjA1cimuw</t>
+          <t>y4XnAL1Mj08</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Websites for Students</t>
+          <t>Free ppt in hindi</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Make Free PPT in Hindi</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Websites for Students</t>
+          <t>Make Free PPT in Hindi</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/C1B3Ajh33XQ</t>
+          <t>rWBWzSvfSLg</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>3 Super Useful Websites for Students</t>
+          <t>Free presentations</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Super+Useful+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Super Useful Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Make Free Presentations</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3 Super Useful Websites for Students</t>
+          <t>Make Free Presentations</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/a3X61bqSoQI</t>
+          <t>Rzw14Mn7zNE</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Science Students</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Websites+for+Science+Students</t>
+          <t>https://notion.so</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Websites for Science Students</t>
+          <t>All-in-one workspace for student notes, syllabi, assignment trackers, and wikis.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Science Students</t>
+          <t>Learn any Topic in 5 Minutes</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zQXPO7Nnqlc</t>
+          <t>https://www.youtube.com/shorts/CVX6Gex7YB8</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Students</t>
+          <t>Sign up for aws builder center toda</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Websites+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Websites for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Sign up for AWS Builder Center today and stop waiting to feel ready</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Students</t>
+          <t>Sign up for AWS Builder Center today and stop waiting to feel ready</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OcFOzIVn0Lw</t>
+          <t>https://www.youtube.com/shorts/M0FPywzjXLc</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3 Websites for Competitive Exam Preparation</t>
+          <t>Sirf 5 mint. mein assignments ready</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Websites+for+Competitive+Exam+Preparation</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Websites for Competitive Exam Preparation</t>
+          <t>Online productivity web tool featured in StudyTools: Sirf 5 Mint. mein Assignments Ready</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>3 Websites for Competitive Exam Preparation</t>
+          <t>Sirf 5 Mint. mein Assignments Ready</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/4xpg4wjBKUs</t>
+          <t>https://www.youtube.com/shorts/N2NQIg3F-k8</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>4 Govt. Websites for Students</t>
+          <t>TypeRacer</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Govt+Websites+for+Students</t>
+          <t>https://play.typeracer.com</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Govt. Websites for Students</t>
+          <t>Multiplayer online typing competition game to test and improve words-per-minute speed.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4 Govt. Websites for Students</t>
+          <t>3 Best Websites for Learning Typing</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/3dAsGVFSMxw</t>
+          <t>https://www.youtube.com/shorts/l2LyfnX-zUE</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>⚡ Productivity &amp; Document Tools</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>4 Hidden Secrets for Students</t>
+          <t>Your tech network before you need it</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Hidden+Secrets+for+Students</t>
+          <t>https://tinywow.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Hidden Secrets for Students</t>
+          <t>Online productivity web tool featured in StudyTools: Build Your Tech Network Before You Need It</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>4 Hidden Secrets for Students</t>
+          <t>Build Your Tech Network Before You Need It</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/qZtvbxYP5RY</t>
+          <t>#AWSBrandPartner</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>🎨 Design, 3D &amp; Graphics</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Commerce Students</t>
+          <t>Free infographics</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Useful+Websites+for+Commerce+Students</t>
+          <t>https://toools.design</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Useful Websites for Commerce Students</t>
+          <t>Creative design web tool featured in StudyTools: Make Free Infographics</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Commerce Students</t>
+          <t>Make Free Infographics</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OJMyRutYkQc</t>
+          <t>#study #students #infographic</t>
         </is>
       </c>
     </row>
@@ -1257,27 +1257,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Science Students</t>
+          <t>3 best apps for science students</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Useful+Websites+for+Science+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Useful Websites for Science Students</t>
+          <t>Developer software platform featured in StudyTools: 3 Best Apps for Science Students</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Science Students</t>
+          <t>3 Best Apps for Science Students</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/w5BrLk7UsTg</t>
+          <t>https://www.youtube.com/shorts/zLQrSHI_uLk</t>
         </is>
       </c>
     </row>
@@ -1289,27 +1289,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>4 Websites for Competitive Exams</t>
+          <t>3 best apps for students</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Websites+for+Competitive+Exams</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Websites for Competitive Exams</t>
+          <t>Developer software platform featured in StudyTools: 3 Best Apps for Students</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4 Websites for Competitive Exams</t>
+          <t>3 Best Apps for Students</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tCgsLqf3bfo</t>
+          <t>https://www.youtube.com/shorts/mb_zeGokqfA</t>
         </is>
       </c>
     </row>
@@ -1321,27 +1321,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>4 Websites for Hindi Medium Students</t>
+          <t>3 secret apps for students</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Websites+for+Hindi+Medium+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Websites for Hindi Medium Students</t>
+          <t>Developer software platform featured in StudyTools: 3 Secret Apps for Students</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>4 Websites for Hindi Medium Students</t>
+          <t>3 Secret Apps for Students</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/XN-jcGcjYaE</t>
+          <t>https://www.youtube.com/shorts/xXouxvwQ0OM</t>
         </is>
       </c>
     </row>
@@ -1353,27 +1353,27 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>5 Amazing Websites for Coding Students</t>
+          <t>3 trending websites for students</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Amazing+Websites+for+Coding+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Amazing Websites for Coding Students</t>
+          <t>Developer software platform featured in StudyTools: 3 Trending Websites for Students</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5 Amazing Websites for Coding Students</t>
+          <t>3 Trending Websites for Students</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/_wMcM12wOMc</t>
+          <t>https://www.youtube.com/shorts/nOQ-rfp8cWo</t>
         </is>
       </c>
     </row>
@@ -1385,27 +1385,27 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>5 Best Websites for Students</t>
+          <t>3 useful apps for medical students</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Best+Websites+for+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Best Websites for Students</t>
+          <t>Developer software platform featured in StudyTools: 3 Useful Apps for Medical Students</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>5 Best Websites for Students</t>
+          <t>3 Useful Apps for Medical Students</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/7U6n4fKnSLg</t>
+          <t>https://www.youtube.com/shorts/FlzAj8JaYEk</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>5 Secret Websites for Students</t>
+          <t>5 amazing websites for coding students</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Secret+Websites+for+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Secret Websites for Students</t>
+          <t>Developer software platform featured in StudyTools: 5 Amazing Websites for Coding Students</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5 Secret Websites for Students</t>
+          <t>5 Amazing Websites for Coding Students</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/1dUmo_oxPJ4</t>
+          <t>https://www.youtube.com/shorts/_wMcM12wOMc</t>
         </is>
       </c>
     </row>
@@ -1449,27 +1449,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>5 Useful Websites for Students</t>
+          <t>5 useful websites for coding students</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Useful+Websites+for+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Useful Websites for Students</t>
+          <t>Developer software platform featured in StudyTools: 5 Useful Websites for Coding Students</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>5 Useful Websites for Students</t>
+          <t>5 Useful Websites for Coding Students</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Q-PV6m2vwwo</t>
+          <t>https://www.youtube.com/shorts/OGwObCfbV8s</t>
         </is>
       </c>
     </row>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>5 Websites for UPSC Students</t>
+          <t>Amazing app for medical students</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Websites+for+UPSC+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Websites for UPSC Students</t>
+          <t>Developer software platform featured in StudyTools: Amazing App for Medical Students</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5 Websites for UPSC Students</t>
+          <t>Amazing App for Medical Students</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5TynzYqZtAw</t>
+          <t>https://www.youtube.com/shorts/jcrZsZFLcwY</t>
         </is>
       </c>
     </row>
@@ -1513,27 +1513,27 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>7 Useful Websites for Students</t>
+          <t>Amazing app for physics students</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=7+Useful+Websites+for+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 7 Useful Websites for Students</t>
+          <t>Developer software platform featured in StudyTools: Amazing App for Physics Students</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>7 Useful Websites for Students</t>
+          <t>Amazing App for Physics Students</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tA_4nryjXqM</t>
+          <t>https://www.youtube.com/shorts/jKpgtngcmbo</t>
         </is>
       </c>
     </row>
@@ -1545,27 +1545,27 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>8 Best Websites for Students</t>
+          <t>Best app for nda students</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=8+Best+Websites+for+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 8 Best Websites for Students</t>
+          <t>Developer software platform featured in StudyTools: Best app for NDA Students</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8 Best Websites for Students</t>
+          <t>Best app for NDA Students</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/YoiMl-Jbwbg</t>
+          <t>https://www.youtube.com/shorts/nvEgPl3HKoQ</t>
         </is>
       </c>
     </row>
@@ -1577,27 +1577,27 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>99% Students Don't Know</t>
+          <t>Best app for students</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=99+Students+Dont+Know</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 99% Students Don't Know</t>
+          <t>Developer software platform featured in StudyTools: Best App for Students</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>99% Students Don't Know</t>
+          <t>Best App for Students</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Iyk4yQpwUqw</t>
+          <t>https://www.youtube.com/shorts/DGNmthKvWrw</t>
         </is>
       </c>
     </row>
@@ -1609,27 +1609,27 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Amazing Website For Students</t>
+          <t>Engineering karni hai ? jaldi apply karo</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+Website+For+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing Website For Students</t>
+          <t>Developer software platform featured in StudyTools: Engineering Karni Hai ? Jaldi Apply karo</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Amazing Website For Students</t>
+          <t>Engineering Karni Hai ? Jaldi Apply karo</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/aCCLhjCKC68</t>
+          <t>https://www.youtube.com/shorts/nRHHCmSt5k0</t>
         </is>
       </c>
     </row>
@@ -1641,27 +1641,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Govt. Exams</t>
+          <t>Free tv remote app</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Govt+Exams</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Govt. Exams</t>
+          <t>Developer software platform featured in StudyTools: Free TV Remote App</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Govt. Exams</t>
+          <t>Free TV Remote App</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Ry4OEaeLFxA</t>
+          <t>https://www.youtube.com/shorts/LEyzUWfxhf8</t>
         </is>
       </c>
     </row>
@@ -1673,27 +1673,27 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Previous Year Question Paper</t>
+          <t>Useful app for students</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Previous+Year+Question+Papers</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Previous Year Question Papers</t>
+          <t>Developer software platform featured in StudyTools: Useful App for Students</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Previous Year Question Papers</t>
+          <t>Useful App for Students</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/GjrM-ccLJH4</t>
+          <t>https://www.youtube.com/shorts/JYuDTJlDfrE</t>
         </is>
       </c>
     </row>
@@ -1705,347 +1705,347 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Students</t>
+          <t>Useful tools for students - don't miss</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Students</t>
+          <t>https://replit.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Students</t>
+          <t>Developer software platform featured in StudyTools: Useful tools for Students - Don't Miss</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Students</t>
+          <t>Useful tools for Students - Don't Miss</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-piHhvqw1ek</t>
+          <t>https://www.youtube.com/shorts/zWapI3Kdek8</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Download Previous Year Question Papers free</t>
+          <t>02 amazing tricks for students</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Download+Previous+Year+Question+Papers+free</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Download Previous Year Question Papers free</t>
+          <t>Educational study resource featured in StudyTools: 02 Amazing Tricks for Students</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Download Previous Year Question Papers free</t>
+          <t>02 Amazing Tricks for Students</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/_HDCNE5Orjs</t>
+          <t>https://www.youtube.com/shorts/7MngAnbw6Bg</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Hidden Website for Students</t>
+          <t>02 hidden secrets for students</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Hidden+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Hidden Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 02 Hidden Secrets for Students</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Hidden Website for Students</t>
+          <t>02 Hidden Secrets for Students</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/YlU6kEh_IPI</t>
+          <t>https://www.youtube.com/shorts/uBKqX2BH9p8</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Important Website for Students</t>
+          <t>03 interesting websites for medical</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Important+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Important Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 03 Interesting Websites for Medical Students</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Important Website for Students</t>
+          <t>03 Interesting Websites for Medical Students</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OG9k9OmgE3w</t>
+          <t>https://www.youtube.com/shorts/7NriigOHXFM</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Most Useful Website for Students</t>
+          <t>03 secret websites for students</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Most+Useful+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Most Useful Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 03 Secret Websites for Students</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Most Useful Website for Students</t>
+          <t>03 Secret Websites for Students</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/aWh4js8RaXs</t>
+          <t>https://www.youtube.com/shorts/c8s9y9ihRgM</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>New Google Website for Students</t>
+          <t>03 useful websites for students</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=New+Google+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: New Google Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 03 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>New Google Website for Students</t>
+          <t>03 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/4ZbPwiN9izA</t>
+          <t>https://www.youtube.com/shorts/QqOuf147caI</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Powerful Website for Students</t>
+          <t>04 useful websites for science students</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Powerful+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Powerful Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 04 Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Powerful Website for Students</t>
+          <t>04 Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/xUyRnMAnXX4</t>
+          <t>https://www.youtube.com/shorts/ucOnI6NjcfI</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Secret Website for Students</t>
+          <t>10 useful websites for students</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secret+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Secret Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 10 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Secret Website for Students</t>
+          <t>10 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/_1I5Pqu1Rcc</t>
+          <t>https://www.youtube.com/shorts/IGsXbv52QC8</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Sirf 5 Mint. mein Assignments Ready</t>
+          <t>2 best websites for medical students</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Sirf+5+Mint+mein+Assignments+Ready</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Sirf 5 Mint. mein Assignments Ready</t>
+          <t>Educational study resource featured in StudyTools: 2 Best Websites for Medical Students</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Sirf 5 Mint. mein Assignments Ready</t>
+          <t>2 Best Websites for Medical Students</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/N2NQIg3F-k8</t>
+          <t>https://www.youtube.com/shorts/2S54YX4wp9Y</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Toppers will never tell</t>
+          <t>2 best websites for science students</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Toppers+will+never+tell</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Toppers will never tell</t>
+          <t>Educational study resource featured in StudyTools: 2 Best Websites for Science Students</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Toppers will never tell</t>
+          <t>2 Best Websites for Science Students</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/miEo8vsfiJ4</t>
+          <t>https://www.youtube.com/shorts/C_7hfKL_yY0</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>💻 Coding &amp; Web Development</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Useful Website for Students</t>
+          <t>2 best websites for ssc and railway</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Useful Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Best Websites for SSC and Railway Exams</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Useful Website for Students</t>
+          <t>2 Best Websites for SSC and Railway Exams</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/pg96CiTtC1Q</t>
+          <t>https://www.youtube.com/shorts/5Okv8eX3SFE</t>
         </is>
       </c>
     </row>
@@ -2057,27 +2057,27 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>02 Amazing Tricks for Students</t>
+          <t>2 biggest secrets for students</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=02+Amazing+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 02 Amazing Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Biggest Secrets for Students</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>02 Amazing Tricks for Students</t>
+          <t>2 Biggest Secrets for Students</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/7MngAnbw6Bg</t>
+          <t>https://www.youtube.com/shorts/rt8mLZCbKFc</t>
         </is>
       </c>
     </row>
@@ -2089,27 +2089,27 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>02 Hidden Secrets for Students</t>
+          <t>2 google tricks for students</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=02+Hidden+Secrets+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 02 Hidden Secrets for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Google Tricks for Students</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>02 Hidden Secrets for Students</t>
+          <t>2 Google Tricks for Students</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/uBKqX2BH9p8</t>
+          <t>https://www.youtube.com/shorts/PUQOc7wUQb0</t>
         </is>
       </c>
     </row>
@@ -2121,27 +2121,27 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>04 Useful Websites for Science Students</t>
+          <t>2 hidden hacks for students</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=04+Useful+Websites+for+Science+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 04 Useful Websites for Science Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Hidden Hacks for Students</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>04 Useful Websites for Science Students</t>
+          <t>2 Hidden Hacks for Students</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ucOnI6NjcfI</t>
+          <t>https://www.youtube.com/shorts/zaldSP8X8Qs</t>
         </is>
       </c>
     </row>
@@ -2153,27 +2153,27 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>2 Best Websites for Science Students</t>
+          <t>2 hidden secrets for students</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Best+Websites+for+Science+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Best Websites for Science Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Hidden Secrets for Students</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2 Best Websites for Science Students</t>
+          <t>2 Hidden Secrets for Students</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/C_7hfKL_yY0</t>
+          <t>https://www.youtube.com/shorts/Ext9KqDmpZs</t>
         </is>
       </c>
     </row>
@@ -2185,27 +2185,27 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2 Google Tricks for Students</t>
+          <t>2 hidden tricks for students</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Google+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Google Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Hidden Tricks For Students</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2 Google Tricks for Students</t>
+          <t>2 Hidden Tricks For Students</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/PUQOc7wUQb0</t>
+          <t>https://www.youtube.com/shorts/c8PzQWwhK5A</t>
         </is>
       </c>
     </row>
@@ -2217,27 +2217,27 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>2 Hidden Hacks for Students</t>
+          <t>2 secret &amp; useful websites for students</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Hidden+Hacks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Hidden Hacks for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Secret &amp; Useful Websites for Students</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2 Hidden Hacks for Students</t>
+          <t>2 Secret &amp; Useful Websites for Students</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zaldSP8X8Qs</t>
+          <t>https://www.youtube.com/shorts/JidBL5RZUmg</t>
         </is>
       </c>
     </row>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2 Hidden Secrets for Students</t>
+          <t>2 secret ai tools for students</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Hidden+Secrets+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Hidden Secrets for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2 Hidden Secrets for Students</t>
+          <t>2 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Ext9KqDmpZs</t>
+          <t>https://www.youtube.com/shorts/0ez5YlRNaTk</t>
         </is>
       </c>
     </row>
@@ -2281,27 +2281,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>2 Hidden Tricks For Students</t>
+          <t>2 secret hacks for students</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Hidden+Tricks+For+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Hidden Tricks For Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Secret Hacks for Students</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2 Hidden Tricks For Students</t>
+          <t>2 Secret Hacks for Students</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/c8PzQWwhK5A</t>
+          <t>https://www.youtube.com/shorts/dz5ZIo1i37c</t>
         </is>
       </c>
     </row>
@@ -2313,27 +2313,27 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2 Secret AI tools for Students</t>
+          <t>2 secret websites for students</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret+AI+tools+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret AI tools for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Secret Websites for Students</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2 Secret AI tools for Students</t>
+          <t>2 Secret Websites for Students</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0ez5YlRNaTk</t>
+          <t>https://www.youtube.com/shorts/oELX1oMG0aM</t>
         </is>
       </c>
     </row>
@@ -2345,27 +2345,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>2 Secret Hacks for Students</t>
+          <t>2 secrets tricks for students</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret+Hacks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret Hacks for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Secrets Tricks for Students</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2 Secret Hacks for Students</t>
+          <t>2 Secrets Tricks for Students</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/dz5ZIo1i37c</t>
+          <t>https://www.youtube.com/shorts/6qup-Rn_U6U</t>
         </is>
       </c>
     </row>
@@ -2377,27 +2377,27 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2 Secret Websites for Students</t>
+          <t>2 useful websites for competitive exams</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret+Websites+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret Websites for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Useful Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2 Secret Websites for Students</t>
+          <t>2 Useful Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/oELX1oMG0aM</t>
+          <t>https://www.youtube.com/shorts/s1RFISlUv7s</t>
         </is>
       </c>
     </row>
@@ -2409,27 +2409,27 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>2 Secrets Tricks for Students</t>
+          <t>2 useful websites for students</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secrets+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secrets Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 2 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2 Secrets Tricks for Students</t>
+          <t>2 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/6qup-Rn_U6U</t>
+          <t>https://www.youtube.com/shorts/cPEdOw3187o</t>
         </is>
       </c>
     </row>
@@ -2441,27 +2441,27 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2 Useful Websites for Competitive Exams</t>
+          <t>2 websites for students</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Useful+Websites+for+Competitive+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Useful Websites for Competitive Exams</t>
+          <t>Educational study resource featured in StudyTools: 2 Websites for Students</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2 Useful Websites for Competitive Exams</t>
+          <t>2 Websites for Students</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/s1RFISlUv7s</t>
+          <t>https://www.youtube.com/shorts/jv0UexkG36A</t>
         </is>
       </c>
     </row>
@@ -2473,17 +2473,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>3 Amazing Gemini Tricks for Students</t>
+          <t>3 amazing gemini tricks for students</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Amazing+Gemini+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Amazing Gemini Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Amazing Gemini Tricks for Students</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -2505,17 +2505,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>3 Amazing Search Terms For Students</t>
+          <t>3 amazing search terms for students</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Amazing+Search+Terms+For+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Amazing Search Terms For Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Amazing Search Terms For Students</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>3 Amazing Tricks for Students</t>
+          <t>3 amazing tricks for students</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Amazing+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Amazing Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Amazing Tricks for Students</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -2569,27 +2569,27 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>3 Best Apps for Science Students</t>
+          <t>3 amazing websites for students</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Best+Apps+for+Science+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Best Apps for Science Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Amazing Websites for Students</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>3 Best Apps for Science Students</t>
+          <t>3 Amazing Websites for Students</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zLQrSHI_uLk</t>
+          <t>https://www.youtube.com/shorts/1X4eiFCwD7s</t>
         </is>
       </c>
     </row>
@@ -2601,27 +2601,27 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>3 Best Apps for Students</t>
+          <t>3 best websites for competitive exams</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Best+Apps+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Best Apps for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Best Websites for competitive exams</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>3 Best Apps for Students</t>
+          <t>3 Best Websites for competitive exams</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/mb_zeGokqfA</t>
+          <t>https://www.youtube.com/shorts/hl_h2ZcNJrk</t>
         </is>
       </c>
     </row>
@@ -2633,27 +2633,27 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>3 Google Search Tricks for Students</t>
+          <t>3 best websites for students</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Google+Search+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Google Search Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Best Websites for Students</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>3 Google Search Tricks for Students</t>
+          <t>3 Best Websites for Students</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/g7ZJc9GNYGM</t>
+          <t>https://www.youtube.com/shorts/ABWjA1cimuw</t>
         </is>
       </c>
     </row>
@@ -2665,27 +2665,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Apps for Students</t>
+          <t>3 google search tricks for students</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Apps+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Apps for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Google Search Tricks for Students</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Apps for Students</t>
+          <t>3 Google Search Tricks for Students</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/xXouxvwQ0OM</t>
+          <t>https://www.youtube.com/shorts/g7ZJc9GNYGM</t>
         </is>
       </c>
     </row>
@@ -2697,17 +2697,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>3 Secret Google Tricks for Students</t>
+          <t>3 secret google tricks for students</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Google+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Google Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Secret Google Tricks for Students</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2729,17 +2729,17 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Study Hacks</t>
+          <t>3 secret study hacks</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Study+Hacks</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Study Hacks</t>
+          <t>Educational study resource featured in StudyTools: 3 Secret Study Hacks</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>3 Secret Tricks for Students</t>
+          <t>3 secret tricks for students</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Secret Tricks for Students</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Websites for Commerce Students</t>
+          <t>3 secret websites for commerce students</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Websites+for+Commerce+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Websites for Commerce Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Secret Websites for Commerce Students</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -2825,27 +2825,27 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>3 Smart Ways to Make Study Notes</t>
+          <t>3 secret websites for medical students</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Smart+Ways+to+Make+Study+Notes</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Smart Ways to Make Study Notes</t>
+          <t>Educational study resource featured in StudyTools: 3 Secret Websites for Medical Students</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>3 Smart Ways to Make Study Notes</t>
+          <t>3 Secret Websites for Medical Students</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/g7UU1eOG4_0</t>
+          <t>https://www.youtube.com/shorts/WUeUBXQa3Jk</t>
         </is>
       </c>
     </row>
@@ -2857,27 +2857,27 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Tricks for Students</t>
+          <t>3 secret websites for students</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Secret Websites for Students</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Tricks for Students</t>
+          <t>3 Secret Websites for Students</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/6m2xitF0R_4</t>
+          <t>https://www.youtube.com/shorts/C1B3Ajh33XQ</t>
         </is>
       </c>
     </row>
@@ -2889,27 +2889,27 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>4 Free Websites for Exam Help</t>
+          <t>3 smart ways to make study notes</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Free+Websites+for+Exam+Help</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Free Websites for Exam Help</t>
+          <t>Educational study resource featured in StudyTools: 3 Smart Ways to Make Study Notes</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>4 Free Websites for Exam Help</t>
+          <t>3 Smart Ways to Make Study Notes</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/GpIzY-UbJ4w</t>
+          <t>https://www.youtube.com/shorts/g7UU1eOG4_0</t>
         </is>
       </c>
     </row>
@@ -2921,27 +2921,27 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Students</t>
+          <t>3 super useful websites for students</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Useful+Websites+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Useful Websites for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Super Useful Websites for Students</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Students</t>
+          <t>3 Super Useful Websites for Students</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/NnjAPKq5rnU</t>
+          <t>https://www.youtube.com/shorts/a3X61bqSoQI</t>
         </is>
       </c>
     </row>
@@ -2953,27 +2953,27 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>5 Free Websites for Competitive Exams</t>
+          <t>3 useful tricks for students</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Free+Websites+for+Competitive+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Free Websites for Competitive Exams</t>
+          <t>Educational study resource featured in StudyTools: 3 Useful Tricks for Students</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>5 Free Websites for Competitive Exams</t>
+          <t>3 Useful Tricks for Students</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Qk9n7RbP9Mc</t>
+          <t>https://www.youtube.com/shorts/6m2xitF0R_4</t>
         </is>
       </c>
     </row>
@@ -2985,27 +2985,27 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>5 Useful Websites for Coding Students</t>
+          <t>3 useful websites for arts students</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Useful+Websites+for+Coding+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Useful Websites for Coding Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Useful Websites for Arts Students</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>5 Useful Websites for Coding Students</t>
+          <t>3 Useful Websites for Arts Students</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OGwObCfbV8s</t>
+          <t>https://www.youtube.com/shorts/IYtWNLqkeLg</t>
         </is>
       </c>
     </row>
@@ -3017,27 +3017,27 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>5 Useful Websites for Students</t>
+          <t>3 useful websites for college students</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Useful+Websites+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Useful Websites for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Useful Websites for College Students</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>5 Useful Websites for Students</t>
+          <t>3 Useful Websites for College Students</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/g8WeFqDnSJA</t>
+          <t>https://www.youtube.com/shorts/oJcGJXsab14</t>
         </is>
       </c>
     </row>
@@ -3049,27 +3049,27 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>99% Students Don't Know</t>
+          <t>3 useful websites for science students</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=99+Students+Dont+Know</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 99% Students Don't Know</t>
+          <t>Educational study resource featured in StudyTools: 3 Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>99% Students Don't Know</t>
+          <t>3 Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/J6OWsj6ByyA</t>
+          <t>https://www.youtube.com/shorts/zQXPO7Nnqlc</t>
         </is>
       </c>
     </row>
@@ -3081,27 +3081,27 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>99% Students Don't Know 6 Amazing Websites fo</t>
+          <t>3 useful websites for students</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=99+Students+Dont+Know+6+Amazing+Websites+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 99% Students Don't Know 6 Amazing Websites for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>99% Students Don't Know 6 Amazing Websites for Students</t>
+          <t>3 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Pw45_9MqFI8</t>
+          <t>https://www.youtube.com/shorts/OcFOzIVn0Lw</t>
         </is>
       </c>
     </row>
@@ -3113,27 +3113,27 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Best Ai Hack for Students</t>
+          <t>3 websites for competitive exams</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Ai+Hack+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Ai Hack for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Best Ai Hack for Students</t>
+          <t>3 Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Sq4K053HECI</t>
+          <t>https://www.youtube.com/shorts/qHDRe3GEZJg</t>
         </is>
       </c>
     </row>
@@ -3145,27 +3145,27 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Best App for Students</t>
+          <t>3 websites for medical students</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+App+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best App for Students</t>
+          <t>Educational study resource featured in StudyTools: 3 Websites for Medical Students</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Best App for Students</t>
+          <t>3 Websites for Medical Students</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/oQCSJpMTe3E</t>
+          <t>https://www.youtube.com/shorts/e_OTFvt2VNI</t>
         </is>
       </c>
     </row>
@@ -3177,27 +3177,27 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Best Study Hack for Students</t>
+          <t>4 free websites for exam help</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Study+Hack+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Study Hack for Students</t>
+          <t>Educational study resource featured in StudyTools: 4 Free Websites for Exam Help</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Best Study Hack for Students</t>
+          <t>4 Free Websites for Exam Help</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/9x6_7Q7edvg</t>
+          <t>https://www.youtube.com/shorts/GpIzY-UbJ4w</t>
         </is>
       </c>
     </row>
@@ -3209,27 +3209,27 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Best Study Hacks for Students</t>
+          <t>4 govt. websites for students</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Study+Hacks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Study Hacks for Students</t>
+          <t>Educational study resource featured in StudyTools: 4 Govt. Websites for Students</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Best Study Hacks for Students</t>
+          <t>4 Govt. Websites for Students</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/6rCa-2mdtwI</t>
+          <t>https://www.youtube.com/shorts/3dAsGVFSMxw</t>
         </is>
       </c>
     </row>
@@ -3241,27 +3241,27 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Competitive Exams</t>
+          <t>4 hidden secrets for students</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Competitive+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Competitive Exams</t>
+          <t>Educational study resource featured in StudyTools: 4 Hidden Secrets for Students</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Competitive Exams</t>
+          <t>4 Hidden Secrets for Students</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/NJ-LdFEx_Y4</t>
+          <t>https://www.youtube.com/shorts/qZtvbxYP5RY</t>
         </is>
       </c>
     </row>
@@ -3273,27 +3273,27 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Medical Students</t>
+          <t>4 useful websites for commerce students</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Medical+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Medical Students</t>
+          <t>Educational study resource featured in StudyTools: 4 Useful Websites for Commerce Students</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Medical Students</t>
+          <t>4 Useful Websites for Commerce Students</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Z7V86uTwDZ0</t>
+          <t>https://www.youtube.com/shorts/OJMyRutYkQc</t>
         </is>
       </c>
     </row>
@@ -3305,27 +3305,27 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Competitive Exam Preparation Website</t>
+          <t>4 useful websites for competitive exams</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Competitive+Exam+Preparation+Website</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Competitive Exam Preparation Website</t>
+          <t>Educational study resource featured in StudyTools: 4 Useful Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Competitive Exam Preparation Website</t>
+          <t>4 Useful Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/J1y0-evDQuU</t>
+          <t>https://www.youtube.com/shorts/IqbnLI6OYGw</t>
         </is>
       </c>
     </row>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Competitive Exams ke liye Previous Year Quest</t>
+          <t>4 useful websites for science students</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Competitive+Exams+ke+liye+Previous+Year+Question+Papers</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Competitive Exams ke liye Previous Year Question Papers</t>
+          <t>Educational study resource featured in StudyTools: 4 Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Competitive Exams ke liye Previous Year Question Papers</t>
+          <t>4 Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/gnaF_4L7slU</t>
+          <t>https://www.youtube.com/shorts/w5BrLk7UsTg</t>
         </is>
       </c>
     </row>
@@ -3369,27 +3369,27 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Free Website for Exam</t>
+          <t>4 useful websites for students</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Free+Website+for+Exam</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Free Website for Exam</t>
+          <t>Educational study resource featured in StudyTools: 4 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Free Website for Exam</t>
+          <t>4 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/CBaQjROr8P0</t>
+          <t>https://www.youtube.com/shorts/NnjAPKq5rnU</t>
         </is>
       </c>
     </row>
@@ -3401,27 +3401,27 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Gemini 4 Secret Tricks for Students</t>
+          <t>4 websites for competitive exams</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Gemini+4+Secret+Tricks+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Gemini 4 Secret Tricks for Students</t>
+          <t>Educational study resource featured in StudyTools: 4 Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Gemini 4 Secret Tricks for Students</t>
+          <t>4 Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/t-JZJ3ZgDlg</t>
+          <t>https://www.youtube.com/shorts/tCgsLqf3bfo</t>
         </is>
       </c>
     </row>
@@ -3433,27 +3433,27 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Gemini Secret Trick for Students</t>
+          <t>4 websites for hindi medium students</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Gemini+Secret+Trick+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Gemini Secret Trick for Students</t>
+          <t>Educational study resource featured in StudyTools: 4 Websites for Hindi Medium Students</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Gemini Secret Trick for Students</t>
+          <t>4 Websites for Hindi Medium Students</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/S901n1Ypm6I</t>
+          <t>https://www.youtube.com/shorts/XN-jcGcjYaE</t>
         </is>
       </c>
     </row>
@@ -3465,27 +3465,27 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Handwritten Notes Free- 3 Gemini Tricks</t>
+          <t>5 best websites for students</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Handwritten+Notes+Free+3+Gemini+Tricks</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Handwritten Notes Free- 3 Gemini Tricks</t>
+          <t>Educational study resource featured in StudyTools: 5 Best Websites for Students</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Handwritten Notes Free- 3 Gemini Tricks</t>
+          <t>5 Best Websites for Students</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/pr2jS095Dmg</t>
+          <t>https://www.youtube.com/shorts/7U6n4fKnSLg</t>
         </is>
       </c>
     </row>
@@ -3497,27 +3497,27 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Handwritten Notes of all Subjects</t>
+          <t>5 free websites for competitive exams</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Handwritten+Notes+of+all+Subjects</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Handwritten Notes of all Subjects</t>
+          <t>Educational study resource featured in StudyTools: 5 Free Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Handwritten Notes of all Subjects</t>
+          <t>5 Free Websites for Competitive Exams</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-wfHHDJu7_s</t>
+          <t>https://www.youtube.com/shorts/Qk9n7RbP9Mc</t>
         </is>
       </c>
     </row>
@@ -3529,27 +3529,27 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Hidden Secret Hack for Students</t>
+          <t>5 secret websites for students</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Hidden+Secret+Hack+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Hidden Secret Hack for Students</t>
+          <t>Educational study resource featured in StudyTools: 5 Secret Websites for Students</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Hidden Secret Hack for Students</t>
+          <t>5 Secret Websites for Students</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UjyRHCCXoa0</t>
+          <t>https://www.youtube.com/shorts/1dUmo_oxPJ4</t>
         </is>
       </c>
     </row>
@@ -3561,27 +3561,27 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Learn any Topic Easily</t>
+          <t>5 useful websites for students</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Learn+any+Topic+Easily</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Learn any Topic Easily</t>
+          <t>Educational study resource featured in StudyTools: 5 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Learn any Topic Easily</t>
+          <t>5 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/jsaFbHRMBMg</t>
+          <t>https://www.youtube.com/shorts/Q-PV6m2vwwo</t>
         </is>
       </c>
     </row>
@@ -3593,27 +3593,27 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Make Free Mind Maps</t>
+          <t>5 websites for upsc students</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Free+Mind+Maps</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Make Free Mind Maps</t>
+          <t>Educational study resource featured in StudyTools: 5 Websites for UPSC Students</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Make Free Mind Maps</t>
+          <t>5 Websites for UPSC Students</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WMEHuNXqNrE</t>
+          <t>https://www.youtube.com/shorts/5TynzYqZtAw</t>
         </is>
       </c>
     </row>
@@ -3625,27 +3625,27 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Maths Students 3 Useful Websites</t>
+          <t>7 useful websites for students</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Maths+Students+3+Useful+Websites</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Maths Students 3 Useful Websites</t>
+          <t>Educational study resource featured in StudyTools: 7 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Maths Students 3 Useful Websites</t>
+          <t>7 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/pDA1m4gMPNY</t>
+          <t>https://www.youtube.com/shorts/tA_4nryjXqM</t>
         </is>
       </c>
     </row>
@@ -3657,27 +3657,27 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Most Useful Website for Students</t>
+          <t>8 best websites for students</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Most+Useful+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Most Useful Website for Students</t>
+          <t>Educational study resource featured in StudyTools: 8 Best Websites for Students</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Most Useful Website for Students</t>
+          <t>8 Best Websites for Students</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/fLTp6eujtLc</t>
+          <t>https://www.youtube.com/shorts/YoiMl-Jbwbg</t>
         </is>
       </c>
     </row>
@@ -3689,27 +3689,27 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Most Useful for Students</t>
+          <t>8 useful websites for board exams 2026</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Most+Useful+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Most Useful for Students</t>
+          <t>Educational study resource featured in StudyTools: 8 Useful Websites for Board Exams 2026</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Most Useful for Students</t>
+          <t>8 Useful Websites for Board Exams 2026</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/aEHznYpCqSg</t>
+          <t>https://www.youtube.com/shorts/Z9KI8CUgB4o</t>
         </is>
       </c>
     </row>
@@ -3721,27 +3721,27 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>New Gemini Trick for Students</t>
+          <t>99% students don't know</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=New+Gemini+Trick+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: New Gemini Trick for Students</t>
+          <t>Educational study resource featured in StudyTools: 99% Students Don't Know</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>New Gemini Trick for Students</t>
+          <t>99% Students Don't Know</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/3VO5ddA4Nbo</t>
+          <t>https://www.youtube.com/shorts/J6OWsj6ByyA</t>
         </is>
       </c>
     </row>
@@ -3753,27 +3753,27 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Sabko Job Milegi</t>
+          <t>99% students don't know 6 amazing w</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Sabko+Job+Milegi</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Sabko Job Milegi</t>
+          <t>Educational study resource featured in StudyTools: 99% Students Don't Know 6 Amazing Websites for Students</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Sabko Job Milegi</t>
+          <t>99% Students Don't Know 6 Amazing Websites for Students</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/BvvLOLdJ-Wk</t>
+          <t>https://www.youtube.com/shorts/Pw45_9MqFI8</t>
         </is>
       </c>
     </row>
@@ -3785,27 +3785,27 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Secret AI tool for Students</t>
+          <t>All in one file tools free</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secret+AI+tool+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Secret AI tool for Students</t>
+          <t>Educational study resource featured in StudyTools: All in one file tools free</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Secret AI tool for Students</t>
+          <t>All in one file tools free</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Zm8FbIjpVG4</t>
+          <t>https://www.youtube.com/shorts/JDEeuYW0I-o</t>
         </is>
       </c>
     </row>
@@ -3817,27 +3817,27 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Secret Study Method for Students</t>
+          <t>Amazing trick for students</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secret+Study+Method+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Secret Study Method for Students</t>
+          <t>Educational study resource featured in StudyTools: Amazing Trick for Students</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Secret Study Method for Students</t>
+          <t>Amazing Trick for Students</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UcDnIvo4HcM</t>
+          <t>https://www.youtube.com/shorts/GMwid_ihihI</t>
         </is>
       </c>
     </row>
@@ -3849,27 +3849,27 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Secret Website for Students</t>
+          <t>Amazing website for students</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secret+Website+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Secret Website for Students</t>
+          <t>Educational study resource featured in StudyTools: Amazing Website For Students</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Secret Website for Students</t>
+          <t>Amazing Website For Students</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tLyYERbCsxo</t>
+          <t>https://www.youtube.com/shorts/aCCLhjCKC68</t>
         </is>
       </c>
     </row>
@@ -3881,27 +3881,27 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Secret Website for Students Create Mind Maps</t>
+          <t>Best ai hack for students</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Secret+Website+for+Students+Create+Mind+Maps</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Secret Website for Students Create Mind Maps</t>
+          <t>Educational study resource featured in StudyTools: Best Ai Hack for Students</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Secret Website for Students Create Mind Maps</t>
+          <t>Best Ai Hack for Students</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/20hAtBs76OM</t>
+          <t>https://www.youtube.com/shorts/Sq4K053HECI</t>
         </is>
       </c>
     </row>
@@ -3913,27 +3913,27 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Student Secret Hack</t>
+          <t>Best career options for arts students</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Student+Secret+Hack</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Student Secret Hack</t>
+          <t>Educational study resource featured in StudyTools: Best Career Options for Arts Students</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Student Secret Hack</t>
+          <t>Best Career Options for Arts Students</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/xFBwdRDTP7o</t>
+          <t>https://www.youtube.com/shorts/YDjuHSNftpk</t>
         </is>
       </c>
     </row>
@@ -3945,27 +3945,27 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Useful Ai tool for Students</t>
+          <t>Best exam hack</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+Ai+tool+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Useful Ai tool for Students</t>
+          <t>Educational study resource featured in StudyTools: Best Exam Hack</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Useful Ai tool for Students</t>
+          <t>Best Exam Hack</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5Imv85K_370</t>
+          <t>https://www.youtube.com/shorts/csEqGxRNeF4</t>
         </is>
       </c>
     </row>
@@ -3977,27 +3977,27 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Useful App for Students</t>
+          <t>Best study hack for students</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+App+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Useful App for Students</t>
+          <t>Educational study resource featured in StudyTools: Best Study Hack for Students</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Useful App for Students</t>
+          <t>Best Study Hack for Students</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/JYuDTJlDfrE</t>
+          <t>https://www.youtube.com/shorts/9x6_7Q7edvg</t>
         </is>
       </c>
     </row>
@@ -4009,27 +4009,27 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Useful Website for Competitive Exams</t>
+          <t>Best study hacks for students</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+Website+for+Competitive+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Useful Website for Competitive Exams</t>
+          <t>Educational study resource featured in StudyTools: Best Study Hacks for Students</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Useful Website for Competitive Exams</t>
+          <t>Best Study Hacks for Students</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5BIOkwvSF2o</t>
+          <t>https://www.youtube.com/shorts/6rCa-2mdtwI</t>
         </is>
       </c>
     </row>
@@ -4041,27 +4041,27 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Useful Websites for Science Students</t>
+          <t>Best website for competitive exam</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+Websites+for+Science+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Useful Websites for Science Students</t>
+          <t>Educational study resource featured in StudyTools: Best Website for Competitive Exam</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Useful Websites for Science Students</t>
+          <t>Best Website for Competitive Exam</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/souJscuD8aU</t>
+          <t>https://www.youtube.com/shorts/WIXm_qVjms8</t>
         </is>
       </c>
     </row>
@@ -4073,27 +4073,27 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Useful tools for Students - Don't Miss</t>
+          <t xml:space="preserve">Best website for competitive exams </t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+tools+for+Students++Dont+Miss</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Useful tools for Students - Don't Miss</t>
+          <t>Educational study resource featured in StudyTools: Best Website for Competitive Exams and Entrance Exams</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Useful tools for Students - Don't Miss</t>
+          <t>Best Website for Competitive Exams and Entrance Exams</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/zWapI3Kdek8</t>
+          <t>https://www.youtube.com/shorts/halVDigt1BQ</t>
         </is>
       </c>
     </row>
@@ -4105,27 +4105,27 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Website for Competitive Exam Preparation</t>
+          <t>Best website for govt. exams</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Website+for+Competitive+Exam+Preparation</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Website for Competitive Exam Preparation</t>
+          <t>Educational study resource featured in StudyTools: Best Website for Govt. Exams</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Website for Competitive Exam Preparation</t>
+          <t>Best Website for Govt. Exams</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/U40g7ZvR2Ro</t>
+          <t>https://www.youtube.com/shorts/Ry4OEaeLFxA</t>
         </is>
       </c>
     </row>
@@ -4137,27 +4137,27 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Website for Science Students</t>
+          <t>Best website for medical students</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Website+for+Science+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Website for Science Students</t>
+          <t>Educational study resource featured in StudyTools: Best Website for Medical Students</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Website for Science Students</t>
+          <t>Best Website for Medical Students</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/8rnEBHmo0Ts</t>
+          <t>https://www.youtube.com/shorts/HDMQ_0Ae54s</t>
         </is>
       </c>
     </row>
@@ -4169,1947 +4169,1947 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Zettlekasten Study Method Notes</t>
+          <t>Best website for neet students</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Zettlekasten+Study+Method+Notes</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Zettlekasten Study Method Notes</t>
+          <t>Educational study resource featured in StudyTools: Best Website for NEET Students</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Zettlekasten Study Method Notes</t>
+          <t>Best Website for NEET Students</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/qM2f8qsm1Gw</t>
+          <t>https://www.youtube.com/shorts/-dKczaB1gGs</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>03 Interesting Websites for Medical Students</t>
+          <t>Best website for previous year ques</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=03+Interesting+Websites+for+Medical+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 03 Interesting Websites for Medical Students</t>
+          <t>Educational study resource featured in StudyTools: Best Website for Previous Year Question Papers</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>03 Interesting Websites for Medical Students</t>
+          <t>Best Website for Previous Year Question Papers</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/7NriigOHXFM</t>
+          <t>https://www.youtube.com/shorts/GjrM-ccLJH4</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>1 Crore ka Stipend</t>
+          <t>Best website for students</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=1+Crore+ka+Stipend</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 1 Crore ka Stipend</t>
+          <t>Educational study resource featured in StudyTools: Best Website for Students</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>1 Crore ka Stipend</t>
+          <t>Best Website for Students</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/UtRHDDOAGjM</t>
+          <t>https://www.youtube.com/shorts/-piHhvqw1ek</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>12th Ke Baad ?</t>
+          <t>College people will never tell</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=12th+Ke+Baad</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 12th Ke Baad ?</t>
+          <t>Educational study resource featured in StudyTools: College people will never tell</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>12th Ke Baad ?</t>
+          <t>College people will never tell</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/uMsFNowAu-Q</t>
+          <t>https://www.youtube.com/shorts/9NapAK2ivUg</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>2 Best Career Options after 12th</t>
+          <t xml:space="preserve">Competitive exams ke liye previous </t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Best+Career+Options+after+12th</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Best Career Options after 12th</t>
+          <t>Educational study resource featured in StudyTools: Competitive Exams ke liye Previous Year Question Papers</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>2 Best Career Options after 12th</t>
+          <t>Competitive Exams ke liye Previous Year Question Papers</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/hJ9PFgjdg3Y</t>
+          <t>https://www.youtube.com/shorts/gnaF_4L7slU</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2 Best Websites for Medical Students</t>
+          <t>Coursera</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Best+Websites+for+Medical+Students</t>
+          <t>https://coursera.org</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Best Websites for Medical Students</t>
+          <t>Global online learning platform offering courses and professional certificates from top universities.</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>2 Best Websites for Medical Students</t>
+          <t>3 Financial Skills for Students</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/2S54YX4wp9Y</t>
+          <t>https://www.youtube.com/shorts/o3UPIe5noNQ</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>2 Best Websites for NDA Exam Preparation</t>
+          <t>Download previous year question pap</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Best+Websites+for+NDA+Exam+Preparation</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Best Websites for NDA Exam Preparation</t>
+          <t>Educational study resource featured in StudyTools: Download Previous Year Question Papers free</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>2 Best Websites for NDA Exam Preparation</t>
+          <t>Download Previous Year Question Papers free</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/oGziImf2NSY</t>
+          <t>https://www.youtube.com/shorts/_HDCNE5Orjs</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2 Best Websites for SSC and Railway Exams</t>
+          <t>Free flowchart</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Best+Websites+for+SSC+and+Railway+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Best Websites for SSC and Railway Exams</t>
+          <t>Educational study resource featured in StudyTools: Make Free Flowchart</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>2 Best Websites for SSC and Railway Exams</t>
+          <t>Make Free Flowchart</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5Okv8eX3SFE</t>
+          <t>https://www.youtube.com/shorts/4owUB-nCJ14</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>2 High Income Skills</t>
+          <t>Free hand drawn diagrams trick</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+High+Income+Skills</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 High Income Skills</t>
+          <t>Educational study resource featured in StudyTools: Free Hand Drawn Diagrams Trick</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>2 High Income Skills</t>
+          <t>Free Hand Drawn Diagrams Trick</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/yJiBetefazk</t>
+          <t>https://www.youtube.com/shorts/WwNULgVAmqE</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>2 Secret AI tools OMG !</t>
+          <t>Free mind maps</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret+AI+tools+OMG</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret AI tools OMG !</t>
+          <t>Educational study resource featured in StudyTools: Make Free Mind Maps</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>2 Secret AI tools OMG !</t>
+          <t>Make Free Mind Maps</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/XLkUpymwgdU</t>
+          <t>https://www.youtube.com/shorts/WMEHuNXqNrE</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>3 Best Websites for competitive exams</t>
+          <t>Free website for exam</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Best+Websites+for+competitive+exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Best Websites for competitive exams</t>
+          <t>Educational study resource featured in StudyTools: Free Website for Exam</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>3 Best Websites for competitive exams</t>
+          <t>Free Website for Exam</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/hl_h2ZcNJrk</t>
+          <t>https://www.youtube.com/shorts/CBaQjROr8P0</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>3 Financial Skills for Students</t>
+          <t>Gemini 4 secret tricks for students</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Financial+Skills+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Financial Skills for Students</t>
+          <t>Educational study resource featured in StudyTools: Gemini 4 Secret Tricks for Students</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>3 Financial Skills for Students</t>
+          <t>Gemini 4 Secret Tricks for Students</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/o3UPIe5noNQ</t>
+          <t>https://www.youtube.com/shorts/t-JZJ3ZgDlg</t>
         </is>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>3 Job Platforms for Freshers</t>
+          <t>Gemini secret trick for students</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Job+Platforms+for+Freshers</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Job Platforms for Freshers</t>
+          <t>Educational study resource featured in StudyTools: Gemini Secret Trick for Students</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>3 Job Platforms for Freshers</t>
+          <t>Gemini Secret Trick for Students</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-bXAtLlnv_s</t>
+          <t>https://www.youtube.com/shorts/S901n1Ypm6I</t>
         </is>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Websites for Medical Students</t>
+          <t>Google search term for students</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Websites+for+Medical+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Websites for Medical Students</t>
+          <t>Educational study resource featured in StudyTools: Google Search term for students</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Websites for Medical Students</t>
+          <t>Google Search term for students</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WUeUBXQa3Jk</t>
+          <t>https://www.youtube.com/shorts/4Ddj1kezOR4</t>
         </is>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>3 Trending Websites for Students</t>
+          <t>Handwritten notes free- 3 gemini tricks</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Trending+Websites+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Trending Websites for Students</t>
+          <t>Educational study resource featured in StudyTools: Handwritten Notes Free- 3 Gemini Tricks</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>3 Trending Websites for Students</t>
+          <t>Handwritten Notes Free- 3 Gemini Tricks</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/nOQ-rfp8cWo</t>
+          <t>https://www.youtube.com/shorts/pr2jS095Dmg</t>
         </is>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Apps for Medical Students</t>
+          <t>Handwritten notes of all subjects</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Apps+for+Medical+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Apps for Medical Students</t>
+          <t>Educational study resource featured in StudyTools: Handwritten Notes of all Subjects</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Apps for Medical Students</t>
+          <t>Handwritten Notes of all Subjects</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/FlzAj8JaYEk</t>
+          <t>https://www.youtube.com/shorts/-wfHHDJu7_s</t>
         </is>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>3 Useful Websites for College Students</t>
+          <t>Handwritten notes trick</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Websites+for+College+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Websites for College Students</t>
+          <t>Educational study resource featured in StudyTools: Handwritten Notes Trick</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>3 Useful Websites for College Students</t>
+          <t>Handwritten Notes Trick</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/oJcGJXsab14</t>
+          <t>https://www.youtube.com/shorts/090lXY3Bhog</t>
         </is>
       </c>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>3 Websites for Competitive Exams</t>
+          <t>Hidden secret for 12th students</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Websites+for+Competitive+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Websites for Competitive Exams</t>
+          <t>Educational study resource featured in StudyTools: Hidden Secret for 12th Students</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>3 Websites for Competitive Exams</t>
+          <t>Hidden Secret for 12th Students</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/qHDRe3GEZJg</t>
+          <t>https://www.youtube.com/shorts/TBgzF54cGpY</t>
         </is>
       </c>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>3 Websites for Medical Students</t>
+          <t>Hidden secret hack for students</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Websites+for+Medical+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Websites for Medical Students</t>
+          <t>Educational study resource featured in StudyTools: Hidden Secret Hack for Students</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>3 Websites for Medical Students</t>
+          <t>Hidden Secret Hack for Students</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/e_OTFvt2VNI</t>
+          <t>https://www.youtube.com/shorts/UjyRHCCXoa0</t>
         </is>
       </c>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>4 Best Ai for SSC Exam Preparation</t>
+          <t>Hidden website for students</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Best+Ai+for+SSC+Exam+Preparation</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Best Ai for SSC Exam Preparation</t>
+          <t>Educational study resource featured in StudyTools: Hidden Website for Students</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>4 Best Ai for SSC Exam Preparation</t>
+          <t>Hidden Website for Students</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/EeFCypCGNGg</t>
+          <t>https://www.youtube.com/shorts/YlU6kEh_IPI</t>
         </is>
       </c>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>4 High Demand Skills</t>
+          <t>Important website for students</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+High+Demand+Skills</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 High Demand Skills</t>
+          <t>Educational study resource featured in StudyTools: Important Website for Students</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>4 High Demand Skills</t>
+          <t>Important Website for Students</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/BZap4r6NysM</t>
+          <t>https://www.youtube.com/shorts/OG9k9OmgE3w</t>
         </is>
       </c>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Competitive Exams</t>
+          <t>Maths students 3 useful websites</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Useful+Websites+for+Competitive+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Useful Websites for Competitive Exams</t>
+          <t>Educational study resource featured in StudyTools: Maths Students 3 Useful Websites</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Competitive Exams</t>
+          <t>Maths Students 3 Useful Websites</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/IqbnLI6OYGw</t>
+          <t>https://www.youtube.com/shorts/pDA1m4gMPNY</t>
         </is>
       </c>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>4 Zero Balance Bank Accounts</t>
+          <t>Mock test &amp; pyq for competitive exa</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Zero+Balance+Bank+Accounts</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Zero Balance Bank Accounts</t>
+          <t>Educational study resource featured in StudyTools: Mock Test &amp; PYQ for Competitive Exams Free</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>4 Zero Balance Bank Accounts</t>
+          <t>Mock Test &amp; PYQ for Competitive Exams Free</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/8BF0ibAsGTU</t>
+          <t>https://www.youtube.com/shorts/xCvAwDljQho</t>
         </is>
       </c>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>5 Skills That Can Make You Rich</t>
+          <t>Most useful for students</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Skills+That+Can+Make+You+Rich</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Skills That Can Make You Rich</t>
+          <t>Educational study resource featured in StudyTools: Most Useful for Students</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>5 Skills That Can Make You Rich</t>
+          <t>Most Useful for Students</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/35FQ4kAmhEI</t>
+          <t>https://www.youtube.com/shorts/aEHznYpCqSg</t>
         </is>
       </c>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>6 Top Rated Skills</t>
+          <t>Most useful website for students</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=6+Top+Rated+Skills</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 6 Top Rated Skills</t>
+          <t>Educational study resource featured in StudyTools: Most Useful Website for Students</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>6 Top Rated Skills</t>
+          <t>Most Useful Website for Students</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WYpv6tetXog</t>
+          <t>https://www.youtube.com/shorts/aWh4js8RaXs</t>
         </is>
       </c>
     </row>
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>8 Useful Websites for Board Exams 2026</t>
+          <t>New gemini trick for students</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=8+Useful+Websites+for+Board+Exams+2026</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 8 Useful Websites for Board Exams 2026</t>
+          <t>Educational study resource featured in StudyTools: New Gemini Trick for Students</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>8 Useful Websites for Board Exams 2026</t>
+          <t>New Gemini Trick for Students</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Z9KI8CUgB4o</t>
+          <t>https://www.youtube.com/shorts/3VO5ddA4Nbo</t>
         </is>
       </c>
     </row>
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>All in one file tools free</t>
+          <t>New google website for students</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=All+in+one+file+tools+free</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: All in one file tools free</t>
+          <t>Educational study resource featured in StudyTools: New Google Website for Students</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>All in one file tools free</t>
+          <t>New Google Website for Students</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/JDEeuYW0I-o</t>
+          <t>https://www.youtube.com/shorts/4ZbPwiN9izA</t>
         </is>
       </c>
     </row>
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Amazing App for Medical Students</t>
+          <t>No exam for govt jobs ?</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+App+for+Medical+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing App for Medical Students</t>
+          <t>Educational study resource featured in StudyTools: No Exam for Govt Jobs ?</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Amazing App for Medical Students</t>
+          <t>No Exam for Govt Jobs ?</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/jcrZsZFLcwY</t>
+          <t>https://www.youtube.com/shorts/Bf9yT0vJBlI</t>
         </is>
       </c>
     </row>
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Amazing App for Physics Students</t>
+          <t>Powerful website for students</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+App+for+Physics+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing App for Physics Students</t>
+          <t>Educational study resource featured in StudyTools: Powerful Website for Students</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Amazing App for Physics Students</t>
+          <t>Powerful Website for Students</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/jKpgtngcmbo</t>
+          <t>https://www.youtube.com/shorts/xUyRnMAnXX4</t>
         </is>
       </c>
     </row>
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Amazing Trick for Students</t>
+          <t>QuillBot / Jenni AI</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+Trick+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing Trick for Students</t>
+          <t>Top-rated student productivity and research assistant for exam prep and writing.</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Amazing Trick for Students</t>
+          <t>Secret AI tool for Students - Don't Miss</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/GMwid_ihihI</t>
+          <t>https://www.youtube.com/shorts/KD60Q1MFmWc</t>
         </is>
       </c>
     </row>
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Best App for Students</t>
+          <t>Sabko job milegi</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+App+for+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best App for Students</t>
+          <t>Educational study resource featured in StudyTools: Sabko Job Milegi</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Best App for Students</t>
+          <t>Sabko Job Milegi</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/DGNmthKvWrw</t>
+          <t>https://www.youtube.com/shorts/BvvLOLdJ-Wk</t>
         </is>
       </c>
     </row>
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Best Exam Hack</t>
+          <t>Secret study method for students</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Exam+Hack</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Exam Hack</t>
+          <t>Educational study resource featured in StudyTools: Secret Study Method for Students</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Best Exam Hack</t>
+          <t>Secret Study Method for Students</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/csEqGxRNeF4</t>
+          <t>https://www.youtube.com/shorts/UcDnIvo4HcM</t>
         </is>
       </c>
     </row>
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Best Internship after 12th</t>
+          <t>Secret website for students</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Internship+after+12th</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Internship after 12th</t>
+          <t>Educational study resource featured in StudyTools: Secret Website for Students</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Best Internship after 12th</t>
+          <t>Secret Website for Students</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OXk_XhJf_3s</t>
+          <t>https://www.youtube.com/shorts/_1I5Pqu1Rcc</t>
         </is>
       </c>
     </row>
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Best Presentation Maker Ai tool</t>
+          <t xml:space="preserve">Secret website for students create </t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Presentation+Maker+Ai+tool</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Presentation Maker Ai tool</t>
+          <t>Educational study resource featured in StudyTools: Secret Website for Students Create Mind Maps</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Best Presentation Maker Ai tool</t>
+          <t>Secret Website for Students Create Mind Maps</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/YS3WM7wjfrU</t>
+          <t>https://www.youtube.com/shorts/20hAtBs76OM</t>
         </is>
       </c>
     </row>
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Competitive Exam</t>
+          <t>Student secret hack</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Competitive+Exam</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Competitive Exam</t>
+          <t>Educational study resource featured in StudyTools: Student Secret Hack</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Competitive Exam</t>
+          <t>Student Secret Hack</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WIXm_qVjms8</t>
+          <t>https://www.youtube.com/shorts/xFBwdRDTP7o</t>
         </is>
       </c>
     </row>
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Competitive Exams and Entran</t>
+          <t>Topic easily</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Competitive+Exams+and+Entrance+Exams</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Competitive Exams and Entrance Exams</t>
+          <t>Educational study resource featured in StudyTools: Learn any Topic Easily</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Best Website for Competitive Exams and Entrance Exams</t>
+          <t>Learn any Topic Easily</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/halVDigt1BQ</t>
+          <t>https://www.youtube.com/shorts/jsaFbHRMBMg</t>
         </is>
       </c>
     </row>
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Medical Students</t>
+          <t>Toppers will never tell</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Medical+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Medical Students</t>
+          <t>Educational study resource featured in StudyTools: Toppers will never tell</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Medical Students</t>
+          <t>Toppers will never tell</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/HDMQ_0Ae54s</t>
+          <t>https://www.youtube.com/shorts/miEo8vsfiJ4</t>
         </is>
       </c>
     </row>
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Best Website for NEET Students</t>
+          <t>Useful ai tool for students</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+NEET+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for NEET Students</t>
+          <t>Educational study resource featured in StudyTools: Useful Ai tool for Students</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Best Website for NEET Students</t>
+          <t>Useful Ai tool for Students</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-dKczaB1gGs</t>
+          <t>https://www.youtube.com/shorts/5Imv85K_370</t>
         </is>
       </c>
     </row>
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Best app for NDA Students</t>
+          <t>Useful website for competitive exams</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+app+for+NDA+Students</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best app for NDA Students</t>
+          <t>Educational study resource featured in StudyTools: Useful Website for Competitive Exams</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Best app for NDA Students</t>
+          <t>Useful Website for Competitive Exams</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/nvEgPl3HKoQ</t>
+          <t>https://www.youtube.com/shorts/5BIOkwvSF2o</t>
         </is>
       </c>
     </row>
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Build Your Tech Network Before You Need It</t>
+          <t>Useful website for nda students</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Build+Your+Tech+Network+Before+You+Need+It</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Build Your Tech Network Before You Need It</t>
+          <t>Educational study resource featured in StudyTools: Useful website For NDA Students</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Build Your Tech Network Before You Need It</t>
+          <t>Useful website For NDA Students</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>#AWSBrandPartner</t>
+          <t>https://www.youtube.com/shorts/R53Gymc3LYQ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>College people will never tell</t>
+          <t>Useful website for students</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=College+people+will+never+tell</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: College people will never tell</t>
+          <t>Educational study resource featured in StudyTools: Useful Website for Students</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>College people will never tell</t>
+          <t>Useful Website for Students</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/9NapAK2ivUg</t>
+          <t>https://www.youtube.com/shorts/pg96CiTtC1Q</t>
         </is>
       </c>
     </row>
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Engineering Karni Hai ? Jaldi Apply karo</t>
+          <t>Useful websites for science students</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Engineering+Karni+Hai++Jaldi+Apply+karo</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Engineering Karni Hai ? Jaldi Apply karo</t>
+          <t>Educational study resource featured in StudyTools: Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Engineering Karni Hai ? Jaldi Apply karo</t>
+          <t>Useful Websites for Science Students</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/nRHHCmSt5k0</t>
+          <t>https://www.youtube.com/shorts/souJscuD8aU</t>
         </is>
       </c>
     </row>
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Free Hand Drawn Diagrams Trick</t>
+          <t>Website for science students</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Free+Hand+Drawn+Diagrams+Trick</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Free Hand Drawn Diagrams Trick</t>
+          <t>Educational study resource featured in StudyTools: Website for Science Students</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Free Hand Drawn Diagrams Trick</t>
+          <t>Website for Science Students</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WwNULgVAmqE</t>
+          <t>https://www.youtube.com/shorts/8rnEBHmo0Ts</t>
         </is>
       </c>
     </row>
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>📚 Learning, Study &amp; Research</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Free Mock Test</t>
+          <t>Zettlekasten study method notes</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Free+Mock+Test</t>
+          <t>https://quillbot.com</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Free Mock Test</t>
+          <t>Educational study resource featured in StudyTools: Zettlekasten Study Method Notes</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Free Mock Test</t>
+          <t>Zettlekasten Study Method Notes</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>y4XnAL1Mj08</t>
+          <t>https://www.youtube.com/shorts/qM2f8qsm1Gw</t>
         </is>
       </c>
     </row>
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Free TV Remote App</t>
+          <t>02 crazy ai tricks</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Free+TV+Remote+App</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Free TV Remote App</t>
+          <t>AI application featured in StudyTools: 02 Crazy AI tricks</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Free TV Remote App</t>
+          <t>02 Crazy AI tricks</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/LEyzUWfxhf8</t>
+          <t>https://www.youtube.com/shorts/ZHxiJvslfZo</t>
         </is>
       </c>
     </row>
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Free Website for Competitive Exam Preparation</t>
+          <t>02 secret ai tools for students</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Free+Website+for+Competitive+Exam+Preparation</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Free Website for Competitive Exam Preparation</t>
+          <t>AI application featured in StudyTools: 02 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Free Website for Competitive Exam Preparation</t>
+          <t>02 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WUnGQX5mnGE</t>
+          <t>https://www.youtube.com/shorts/FpDS7WohAXM</t>
         </is>
       </c>
     </row>
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Google Search term for students</t>
+          <t>03 chatgpt secret codes - don't miss</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Google+Search+term+for+students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Google Search term for students</t>
+          <t>AI application featured in StudyTools: 03 ChatGPT Secret Codes - Don't Miss</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Google Search term for students</t>
+          <t>03 ChatGPT Secret Codes - Don't Miss</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/4Ddj1kezOR4</t>
+          <t>https://www.youtube.com/shorts/vczLia3I5Uc</t>
         </is>
       </c>
     </row>
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Govt. Exam Preparation ?</t>
+          <t>03 secret ai tools for students</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Govt+Exam+Preparation</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Govt. Exam Preparation ?</t>
+          <t>AI application featured in StudyTools: 03 Secret Ai tools for Students</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Govt. Exam Preparation ?</t>
+          <t>03 Secret Ai tools for Students</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/DOoSMfQIlaA</t>
+          <t>https://www.youtube.com/shorts/YSwb1xgHN2M</t>
         </is>
       </c>
     </row>
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Handwritten Notes Trick</t>
+          <t>2 amazing secrets for students</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Handwritten+Notes+Trick</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Handwritten Notes Trick</t>
+          <t>AI application featured in StudyTools: 2 Amazing Secrets for Students</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Handwritten Notes Trick</t>
+          <t>2 Amazing Secrets for Students</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/090lXY3Bhog</t>
+          <t>https://www.youtube.com/shorts/0ybkdPrykQA</t>
         </is>
       </c>
     </row>
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Hidden Secret for 12th Students</t>
+          <t>2 secret ai tools for students</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Hidden+Secret+for+12th+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Hidden Secret for 12th Students</t>
+          <t>AI application featured in StudyTools: 2 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Hidden Secret for 12th Students</t>
+          <t>2 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/TBgzF54cGpY</t>
+          <t>https://www.youtube.com/shorts/VwDcOtswJRM</t>
         </is>
       </c>
     </row>
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Learn AI Skills for Future Growth</t>
+          <t>2 secret websites for students</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Learn+AI+Skills+for+Future+Growth</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Learn AI Skills for Future Growth</t>
+          <t>AI application featured in StudyTools: 2 Secret Websites for Students</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Learn AI Skills for Future Growth</t>
+          <t>2 Secret Websites for Students</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>w1uSgT_AJ9E</t>
+          <t>https://www.youtube.com/shorts/bHVbJAxRToQ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Make Free Flowchart</t>
+          <t>2 tricks for students</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Free+Flowchart</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Make Free Flowchart</t>
+          <t>AI application featured in StudyTools: 2 Tricks for Students</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Make Free Flowchart</t>
+          <t>2 Tricks for Students</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/4owUB-nCJ14</t>
+          <t>https://www.youtube.com/shorts/oOXBL97FjNI</t>
         </is>
       </c>
     </row>
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Make Free Infographics</t>
+          <t>3 ai tools for coding students</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Free+Infographics</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Make Free Infographics</t>
+          <t>AI application featured in StudyTools: 3 Ai tools for Coding Students</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Make Free Infographics</t>
+          <t>3 Ai tools for Coding Students</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>#study #students #infographic</t>
+          <t>https://www.youtube.com/shorts/0nMv19MCya4</t>
         </is>
       </c>
     </row>
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Make Free PPT in Hindi</t>
+          <t>3 ai tools for students - don't miss</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Free+PPT+in+Hindi</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Make Free PPT in Hindi</t>
+          <t>AI application featured in StudyTools: 3 AI tools for Students - Don't Miss</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Make Free PPT in Hindi</t>
+          <t>3 AI tools for Students - Don't Miss</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>rWBWzSvfSLg</t>
+          <t>https://www.youtube.com/shorts/d2cju2oB-LU</t>
         </is>
       </c>
     </row>
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Make Free Presentations</t>
+          <t>3 amazing ai tools for students</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Make+Free+Presentations</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Make Free Presentations</t>
+          <t>AI application featured in StudyTools: 3 Amazing Ai tools for students</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Make Free Presentations</t>
+          <t>3 Amazing Ai tools for students</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>Rzw14Mn7zNE</t>
+          <t>https://www.youtube.com/shorts/TC_KtvoSgsk</t>
         </is>
       </c>
     </row>
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Mock Test &amp; PYQ for Competitive Exams Free</t>
+          <t>3 amazing websites for students</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Mock+Test++PYQ+for+Competitive+Exams+Free</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Mock Test &amp; PYQ for Competitive Exams Free</t>
+          <t>AI application featured in StudyTools: 3 Amazing Websites for Students</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Mock Test &amp; PYQ for Competitive Exams Free</t>
+          <t>3 Amazing Websites for Students</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/xCvAwDljQho</t>
+          <t>https://www.youtube.com/shorts/5yvrrK8H_0Y</t>
         </is>
       </c>
     </row>
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>No Exam for Govt Jobs ?</t>
+          <t>3 best hacks for students</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=No+Exam+for+Govt+Jobs</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: No Exam for Govt Jobs ?</t>
+          <t>AI application featured in StudyTools: 3 Best Hacks For Students</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>No Exam for Govt Jobs ?</t>
+          <t>3 Best Hacks For Students</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Bf9yT0vJBlI</t>
+          <t>https://www.youtube.com/shorts/miybma9nGQU</t>
         </is>
       </c>
     </row>
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Sign up for AWS Builder Center today and star</t>
+          <t>3 chatgpt codes for students</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Sign+up+for+AWS+Builder+Center+today+and+start+one+saved+Workshop</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Sign up for AWS Builder Center today and start one saved Workshop</t>
+          <t>AI application featured in StudyTools: 3 ChatGPT Codes for Students</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Sign up for AWS Builder Center today and start one saved Workshop</t>
+          <t>3 ChatGPT Codes for Students</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/AytWBcGrDo4</t>
+          <t>https://www.youtube.com/shorts/ia3E6zT1jVc</t>
         </is>
       </c>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Sign up for AWS Builder Center today and stop</t>
+          <t>3 chatgpt secret codes</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Sign+up+for+AWS+Builder+Center+today+and+stop+waiting+to+feel+ready</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Sign up for AWS Builder Center today and stop waiting to feel ready</t>
+          <t>AI application featured in StudyTools: 3 Chatgpt Secret Codes</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Sign up for AWS Builder Center today and stop waiting to feel ready</t>
+          <t>3 Chatgpt Secret Codes</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/M0FPywzjXLc</t>
+          <t>https://www.youtube.com/shorts/mgyrwdckN5E</t>
         </is>
       </c>
     </row>
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Turn EGO into Power</t>
+          <t>3 chatgpt secret codes for students</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Turn+EGO+into+Power</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Turn EGO into Power</t>
+          <t>AI application featured in StudyTools: 3 ChatGPT Secret Codes for Students</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Turn EGO into Power</t>
+          <t>3 ChatGPT Secret Codes for Students</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/uOKnC0dxgzI</t>
+          <t>https://www.youtube.com/shorts/Z1f3mOUfR-Y</t>
         </is>
       </c>
     </row>
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>🛠️ Utilities &amp; Web Tools</t>
+          <t>🤖 AI &amp; Machine Learning Tools</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Useful website For NDA Students</t>
+          <t>3 chatgpt secret codes for study</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Useful+website+For+NDA+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Useful website For NDA Students</t>
+          <t>AI application featured in StudyTools: 3 ChatGPT Secret Codes for Study</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Useful website For NDA Students</t>
+          <t>3 ChatGPT Secret Codes for Study</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/R53Gymc3LYQ</t>
+          <t>https://www.youtube.com/shorts/FjVTjIdIuUg</t>
         </is>
       </c>
     </row>
@@ -6121,27 +6121,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>02 Crazy AI tricks</t>
+          <t>3 chatgpt secret tricks for students</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=02+Crazy+AI+tricks</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 02 Crazy AI tricks</t>
+          <t>AI application featured in StudyTools: 3 Chatgpt Secret Tricks for Students</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>02 Crazy AI tricks</t>
+          <t>3 Chatgpt Secret Tricks for Students</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ZHxiJvslfZo</t>
+          <t>https://www.youtube.com/shorts/u_fZGjSgFxI</t>
         </is>
       </c>
     </row>
@@ -6153,27 +6153,27 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>02 Secret AI tools for Students</t>
+          <t>3 chatgpt tricks for students</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=02+Secret+AI+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 02 Secret AI tools for Students</t>
+          <t>AI application featured in StudyTools: 3 Chatgpt Tricks for Students</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>02 Secret AI tools for Students</t>
+          <t>3 Chatgpt Tricks for Students</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/FpDS7WohAXM</t>
+          <t>https://www.youtube.com/shorts/0hVY2XzwHsc</t>
         </is>
       </c>
     </row>
@@ -6185,27 +6185,27 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>03 ChatGPT Secret Codes - Don't Miss</t>
+          <t>3 gemini hacks for students</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=03+ChatGPT+Secret+Codes++Dont+Miss</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 03 ChatGPT Secret Codes - Don't Miss</t>
+          <t>AI application featured in StudyTools: 3 Gemini Hacks for Students</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>03 ChatGPT Secret Codes - Don't Miss</t>
+          <t>3 Gemini Hacks for Students</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/vczLia3I5Uc</t>
+          <t>https://www.youtube.com/shorts/7H18POO3qyc</t>
         </is>
       </c>
     </row>
@@ -6217,27 +6217,27 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>03 Secret Ai tools for Students</t>
+          <t>3 hidden chatgpt tricks</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=03+Secret+Ai+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 03 Secret Ai tools for Students</t>
+          <t>AI application featured in StudyTools: 3 Hidden ChatGPT Tricks</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>03 Secret Ai tools for Students</t>
+          <t>3 Hidden ChatGPT Tricks</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/YSwb1xgHN2M</t>
+          <t>https://www.youtube.com/shorts/_AAK-ooGRfg</t>
         </is>
       </c>
     </row>
@@ -6249,27 +6249,27 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>2 Amazing Secrets for Students</t>
+          <t>3 hidden study ai hacks</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Amazing+Secrets+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Amazing Secrets for Students</t>
+          <t>AI application featured in StudyTools: 3 Hidden Study AI Hacks</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>2 Amazing Secrets for Students</t>
+          <t>3 Hidden Study AI Hacks</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0ybkdPrykQA</t>
+          <t>https://www.youtube.com/shorts/mTk2FsLia6M</t>
         </is>
       </c>
     </row>
@@ -6281,27 +6281,27 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>2 Best Ai tools for Students</t>
+          <t>3 secret ai tools for students</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Best+Ai+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Best Ai tools for Students</t>
+          <t>AI application featured in StudyTools: 3 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>2 Best Ai tools for Students</t>
+          <t>3 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0mWolQnd5kA</t>
+          <t>https://www.youtube.com/shorts/gmk5TDpHBnY</t>
         </is>
       </c>
     </row>
@@ -6313,27 +6313,27 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>2 Secret AI tools for Students</t>
+          <t>3 secret chatgpt codes</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret+AI+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret AI tools for Students</t>
+          <t>AI application featured in StudyTools: 3 Secret ChatGPT Codes</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>2 Secret AI tools for Students</t>
+          <t>3 Secret ChatGPT Codes</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/VwDcOtswJRM</t>
+          <t>https://www.youtube.com/shorts/kYaOiT6F6hE</t>
         </is>
       </c>
     </row>
@@ -6345,27 +6345,27 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>2 Secret Websites for Students</t>
+          <t>3 secret chatgpt codes for students</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Secret+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Secret Websites for Students</t>
+          <t>AI application featured in StudyTools: 3 Secret Chatgpt codes for Students</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>2 Secret Websites for Students</t>
+          <t>3 Secret Chatgpt codes for Students</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/bHVbJAxRToQ</t>
+          <t>https://www.youtube.com/shorts/kFzOixfWTTs</t>
         </is>
       </c>
     </row>
@@ -6377,27 +6377,27 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>2 Tricks for Students</t>
+          <t>3 secret chatgpt study tricks don't miss</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2+Tricks+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 2 Tricks for Students</t>
+          <t>AI application featured in StudyTools: 3 Secret ChatGPT Study Tricks Don't Miss</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>2 Tricks for Students</t>
+          <t>3 Secret ChatGPT Study Tricks Don't Miss</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/oOXBL97FjNI</t>
+          <t>https://www.youtube.com/shorts/fOgVqmZ3xuE</t>
         </is>
       </c>
     </row>
@@ -6409,27 +6409,27 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>3 AI tools for Students - Don't Miss</t>
+          <t>3 secret websites for students #</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+AI+tools+for+Students++Dont+Miss</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 AI tools for Students - Don't Miss</t>
+          <t>AI application featured in StudyTools: 3 Secret Websites for Students #</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>3 AI tools for Students - Don't Miss</t>
+          <t>3 Secret Websites for Students #</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/d2cju2oB-LU</t>
+          <t>https://www.youtube.com/shorts/AL_i2yBGqiw</t>
         </is>
       </c>
     </row>
@@ -6441,27 +6441,27 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>3 Ai tools for Coding Students</t>
+          <t>3 useful ai tools for students</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Ai+tools+for+Coding+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Ai tools for Coding Students</t>
+          <t>AI application featured in StudyTools: 3 Useful Ai tools for Students</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>3 Ai tools for Coding Students</t>
+          <t>3 Useful Ai tools for Students</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0nMv19MCya4</t>
+          <t>https://www.youtube.com/shorts/6C_qQumATvk</t>
         </is>
       </c>
     </row>
@@ -6473,27 +6473,27 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>3 Amazing Ai tools for students</t>
+          <t>3 useful study websites</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Amazing+Ai+tools+for+students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Amazing Ai tools for students</t>
+          <t>AI application featured in StudyTools: 3 Useful Study Websites</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>3 Amazing Ai tools for students</t>
+          <t>3 Useful Study Websites</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/TC_KtvoSgsk</t>
+          <t>https://www.youtube.com/shorts/aEgd94OcaHA</t>
         </is>
       </c>
     </row>
@@ -6505,27 +6505,27 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>3 Amazing Websites for Students</t>
+          <t>3 useful websites for students</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Amazing+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Amazing Websites for Students</t>
+          <t>AI application featured in StudyTools: 3 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>3 Amazing Websites for Students</t>
+          <t>3 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/5yvrrK8H_0Y</t>
+          <t>https://www.youtube.com/shorts/CFipua2bHHY</t>
         </is>
       </c>
     </row>
@@ -6537,27 +6537,27 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>3 Best AI tools for Students</t>
+          <t>4 chatgpt secret codes</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Best+AI+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Best AI tools for Students</t>
+          <t>AI application featured in StudyTools: 4 ChatGPT Secret Codes</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>3 Best AI tools for Students</t>
+          <t>4 ChatGPT Secret Codes</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/63Q1JUzjPR4</t>
+          <t>https://www.youtube.com/shorts/k9w9AHlFo5o</t>
         </is>
       </c>
     </row>
@@ -6569,27 +6569,27 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>3 Best Hacks For Students</t>
+          <t>4 chatgpt tricks for students</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Best+Hacks+For+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Best Hacks For Students</t>
+          <t>AI application featured in StudyTools: 4 ChatGPT Tricks for Students</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>3 Best Hacks For Students</t>
+          <t>4 ChatGPT Tricks for Students</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/miybma9nGQU</t>
+          <t>https://www.youtube.com/shorts/WZIsf5UQ0IM</t>
         </is>
       </c>
     </row>
@@ -6601,27 +6601,27 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>3 ChatGPT Codes for Students</t>
+          <t>4 hidden &amp; secret websites for students</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+ChatGPT+Codes+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 ChatGPT Codes for Students</t>
+          <t>AI application featured in StudyTools: 4 Hidden &amp; Secret Websites for Students</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>3 ChatGPT Codes for Students</t>
+          <t>4 Hidden &amp; Secret Websites for Students</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ia3E6zT1jVc</t>
+          <t>https://www.youtube.com/shorts/yZdbHrNx_h8</t>
         </is>
       </c>
     </row>
@@ -6633,27 +6633,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>3 ChatGPT Secret Codes for Students</t>
+          <t>4 secret ai tools for students</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+ChatGPT+Secret+Codes+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 ChatGPT Secret Codes for Students</t>
+          <t>AI application featured in StudyTools: 4 Secret Ai tools for Students</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>3 ChatGPT Secret Codes for Students</t>
+          <t>4 Secret Ai tools for Students</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Z1f3mOUfR-Y</t>
+          <t>https://www.youtube.com/shorts/2mfnVGRnHsw</t>
         </is>
       </c>
     </row>
@@ -6665,27 +6665,27 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>3 ChatGPT Secret Codes for Study</t>
+          <t>4 secret chatgpt codes</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+ChatGPT+Secret+Codes+for+Study</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 ChatGPT Secret Codes for Study</t>
+          <t>AI application featured in StudyTools: 4 Secret ChatGPT Codes</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>3 ChatGPT Secret Codes for Study</t>
+          <t>4 Secret ChatGPT Codes</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/FjVTjIdIuUg</t>
+          <t>https://www.youtube.com/shorts/T_qQtVIU_UI</t>
         </is>
       </c>
     </row>
@@ -6697,27 +6697,27 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>3 Chatgpt Secret Codes</t>
+          <t>4 secret websites</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Chatgpt+Secret+Codes</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Chatgpt Secret Codes</t>
+          <t>AI application featured in StudyTools: 4 Secret Websites</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>3 Chatgpt Secret Codes</t>
+          <t>4 Secret Websites</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/mgyrwdckN5E</t>
+          <t>https://www.youtube.com/shorts/3ouy3oj_hds</t>
         </is>
       </c>
     </row>
@@ -6729,27 +6729,27 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>3 Chatgpt Secret Tricks for Students</t>
+          <t>4 secret websites for students</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Chatgpt+Secret+Tricks+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Chatgpt Secret Tricks for Students</t>
+          <t>AI application featured in StudyTools: 4 Secret Websites for Students</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>3 Chatgpt Secret Tricks for Students</t>
+          <t>4 Secret Websites for Students</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/u_fZGjSgFxI</t>
+          <t>https://www.youtube.com/shorts/sYVXDpTbVoo</t>
         </is>
       </c>
     </row>
@@ -6761,27 +6761,27 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>3 Chatgpt Tricks for Students</t>
+          <t>4 useful websites for students</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Chatgpt+Tricks+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Chatgpt Tricks for Students</t>
+          <t>AI application featured in StudyTools: 4 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>3 Chatgpt Tricks for Students</t>
+          <t>4 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/0hVY2XzwHsc</t>
+          <t>https://www.youtube.com/shorts/adjMpbOPI84</t>
         </is>
       </c>
     </row>
@@ -6793,27 +6793,27 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>3 Gemini Hacks for Students</t>
+          <t>5 chatgpt secret codes</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Gemini+Hacks+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Gemini Hacks for Students</t>
+          <t>AI application featured in StudyTools: 5 ChatGPT Secret Codes</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>3 Gemini Hacks for Students</t>
+          <t>5 ChatGPT Secret Codes</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/7H18POO3qyc</t>
+          <t>https://www.youtube.com/shorts/KPRFyCuKvXs</t>
         </is>
       </c>
     </row>
@@ -6825,27 +6825,27 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>3 Hidden ChatGPT Tricks</t>
+          <t>5 gemini secret codes</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Hidden+ChatGPT+Tricks</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Hidden ChatGPT Tricks</t>
+          <t>AI application featured in StudyTools: 5 Gemini Secret Codes</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>3 Hidden ChatGPT Tricks</t>
+          <t>5 Gemini Secret Codes</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/_AAK-ooGRfg</t>
+          <t>https://www.youtube.com/shorts/k7JoNgbUduc</t>
         </is>
       </c>
     </row>
@@ -6857,27 +6857,27 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>3 Hidden Study AI Hacks</t>
+          <t>5 sector ai for students</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Hidden+Study+AI+Hacks</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Hidden Study AI Hacks</t>
+          <t>AI application featured in StudyTools: 5 Sector AI for Students</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>3 Hidden Study AI Hacks</t>
+          <t>5 Sector AI for Students</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/mTk2FsLia6M</t>
+          <t>https://www.youtube.com/shorts/rXr861XdpCc</t>
         </is>
       </c>
     </row>
@@ -6889,27 +6889,27 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>3 Secret AI Hacks for Students</t>
+          <t>6 secret ai tools for students</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+AI+Hacks+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret AI Hacks for Students</t>
+          <t>AI application featured in StudyTools: 6 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>3 Secret AI Hacks for Students</t>
+          <t>6 Secret AI tools for Students</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Sd6MXRC4MIg</t>
+          <t>https://www.youtube.com/shorts/OtJwWNu2k4o</t>
         </is>
       </c>
     </row>
@@ -6921,27 +6921,27 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>3 Secret AI tools for Students</t>
+          <t>7 secret websites for students</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+AI+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret AI tools for Students</t>
+          <t>AI application featured in StudyTools: 7 Secret Websites for Students</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>3 Secret AI tools for Students</t>
+          <t>7 Secret Websites for Students</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/gmk5TDpHBnY</t>
+          <t>https://www.youtube.com/shorts/I0V0V-JuUyA</t>
         </is>
       </c>
     </row>
@@ -6953,27 +6953,27 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>3 Secret ChatGPT Codes</t>
+          <t>7 useful ai tools for students</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+ChatGPT+Codes</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret ChatGPT Codes</t>
+          <t>AI application featured in StudyTools: 7 Useful Ai tools for Students</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>3 Secret ChatGPT Codes</t>
+          <t>7 Useful Ai tools for Students</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/kYaOiT6F6hE</t>
+          <t>https://www.youtube.com/shorts/BVNLM_LAzL4</t>
         </is>
       </c>
     </row>
@@ -6985,27 +6985,27 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>3 Secret ChatGPT Study Tricks Don't Miss</t>
+          <t>7 useful websites for students</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+ChatGPT+Study+Tricks+Dont+Miss</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret ChatGPT Study Tricks Don't Miss</t>
+          <t>AI application featured in StudyTools: 7 Useful Websites for Students</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>3 Secret ChatGPT Study Tricks Don't Miss</t>
+          <t>7 Useful Websites for Students</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/fOgVqmZ3xuE</t>
+          <t>https://www.youtube.com/shorts/fdkf0alHgbE</t>
         </is>
       </c>
     </row>
@@ -7017,27 +7017,27 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Chatgpt codes for Students</t>
+          <t>90% students don't know ?</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Chatgpt+codes+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Chatgpt codes for Students</t>
+          <t>AI application featured in StudyTools: 90% Students Don't Know ?</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>3 Secret Chatgpt codes for Students</t>
+          <t>90% Students Don't Know ?</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/kFzOixfWTTs</t>
+          <t>https://www.youtube.com/shorts/fYnnTa33be0</t>
         </is>
       </c>
     </row>
@@ -7049,27 +7049,27 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>3 Secret Websites for Students #</t>
+          <t>99% students don't know</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Secret+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Secret Websites for Students #</t>
+          <t>AI application featured in StudyTools: 99% Students Don't Know</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>3 Secret Websites for Students #</t>
+          <t>99% Students Don't Know</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/AL_i2yBGqiw</t>
+          <t>https://www.youtube.com/shorts/IHpUMVW47hA</t>
         </is>
       </c>
     </row>
@@ -7081,27 +7081,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Ai tools for Students</t>
+          <t>Amazing &amp; secret ai tool</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Ai+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Ai tools for Students</t>
+          <t>AI application featured in StudyTools: Amazing &amp; Secret Ai tool</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Ai tools for Students</t>
+          <t>Amazing &amp; Secret Ai tool</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/6C_qQumATvk</t>
+          <t>https://www.youtube.com/shorts/vsWCMWnopiI</t>
         </is>
       </c>
     </row>
@@ -7113,27 +7113,27 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>3 Useful Study Websites</t>
+          <t>Amazing ai tool for students</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Study+Websites</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Study Websites</t>
+          <t>AI application featured in StudyTools: Amazing Ai tool for Students</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>3 Useful Study Websites</t>
+          <t>Amazing Ai tool for Students</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/aEgd94OcaHA</t>
+          <t>https://www.youtube.com/shorts/A_PkccGaNoc</t>
         </is>
       </c>
     </row>
@@ -7145,27 +7145,27 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Students</t>
+          <t>Amazing ai tool- don't miss</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=3+Useful+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 3 Useful Websites for Students</t>
+          <t>AI application featured in StudyTools: Amazing Ai tool- Don't Miss</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>3 Useful Websites for Students</t>
+          <t>Amazing Ai tool- Don't Miss</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/CFipua2bHHY</t>
+          <t>https://www.youtube.com/shorts/rv4DX0UMYvo</t>
         </is>
       </c>
     </row>
@@ -7177,27 +7177,27 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>4 Best AI tools for Science Students</t>
+          <t>Amazing trick for students</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Best+AI+tools+for+Science+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Best AI tools for Science Students</t>
+          <t>AI application featured in StudyTools: Amazing Trick for Students</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>4 Best AI tools for Science Students</t>
+          <t>Amazing Trick for Students</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/nz95loGUYQs</t>
+          <t>https://www.youtube.com/shorts/tXPl1YWSf5o</t>
         </is>
       </c>
     </row>
@@ -7209,27 +7209,27 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>4 ChatGPT Secret Codes</t>
+          <t>Amazing website for students</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+ChatGPT+Secret+Codes</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 ChatGPT Secret Codes</t>
+          <t>AI application featured in StudyTools: Amazing Website for Students</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>4 ChatGPT Secret Codes</t>
+          <t>Amazing Website for Students</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/k9w9AHlFo5o</t>
+          <t>https://www.youtube.com/shorts/Cb0wsxJZGK4</t>
         </is>
       </c>
     </row>
@@ -7241,27 +7241,27 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>4 ChatGPT Tricks for Students</t>
+          <t>Average salary 25-30 lacs</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+ChatGPT+Tricks+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 ChatGPT Tricks for Students</t>
+          <t>AI application featured in StudyTools: Average Salary 25-30 Lacs</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>4 ChatGPT Tricks for Students</t>
+          <t>Average Salary 25-30 Lacs</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/WZIsf5UQ0IM</t>
+          <t>https://www.youtube.com/shorts/2O5ZSvgljCk</t>
         </is>
       </c>
     </row>
@@ -7273,27 +7273,27 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>4 Hidden &amp; Secret Websites for Students</t>
+          <t>Best ai app for students</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Hidden++Secret+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Hidden &amp; Secret Websites for Students</t>
+          <t>AI application featured in StudyTools: Best Ai app for Students</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>4 Hidden &amp; Secret Websites for Students</t>
+          <t>Best Ai app for Students</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/yZdbHrNx_h8</t>
+          <t>https://www.youtube.com/shorts/ysnBWYnY_l8</t>
         </is>
       </c>
     </row>
@@ -7305,27 +7305,27 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>4 Secret Ai tools for Students</t>
+          <t>Best ai hack for students</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Secret+Ai+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Secret Ai tools for Students</t>
+          <t>AI application featured in StudyTools: Best Ai hack for Students</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>4 Secret Ai tools for Students</t>
+          <t>Best Ai hack for Students</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/2mfnVGRnHsw</t>
+          <t>https://www.youtube.com/shorts/-ybptTMGa2M</t>
         </is>
       </c>
     </row>
@@ -7337,27 +7337,27 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>4 Secret ChatGPT Codes</t>
+          <t>Best ai tool for students</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Secret+ChatGPT+Codes</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Secret ChatGPT Codes</t>
+          <t>AI application featured in StudyTools: Best AI tool for Students</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>4 Secret ChatGPT Codes</t>
+          <t>Best AI tool for Students</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/T_qQtVIU_UI</t>
+          <t>https://www.youtube.com/shorts/RwiXc1YWloU</t>
         </is>
       </c>
     </row>
@@ -7369,27 +7369,27 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>4 Secret Websites</t>
+          <t xml:space="preserve">Best ai tool for students - topper </t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Secret+Websites</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Secret Websites</t>
+          <t>AI application featured in StudyTools: Best Ai Tool for Students - Topper se aage</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>4 Secret Websites</t>
+          <t>Best Ai Tool for Students - Topper se aage</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/3ouy3oj_hds</t>
+          <t>https://www.youtube.com/shorts/xvYTzAtCrZY</t>
         </is>
       </c>
     </row>
@@ -7401,27 +7401,27 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>4 Secret Websites for Students</t>
+          <t>Best secret app for generating prof</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Secret+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Secret Websites for Students</t>
+          <t>AI application featured in StudyTools: Best Secret app for Generating Profile Pictures</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>4 Secret Websites for Students</t>
+          <t>Best Secret app for Generating Profile Pictures</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/sYVXDpTbVoo</t>
+          <t>https://www.youtube.com/shorts/BwYnj6rWwao</t>
         </is>
       </c>
     </row>
@@ -7433,27 +7433,27 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Students</t>
+          <t>Best website for students</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=4+Useful+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 4 Useful Websites for Students</t>
+          <t>AI application featured in StudyTools: Best Website for Students</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>4 Useful Websites for Students</t>
+          <t>Best Website for Students</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/adjMpbOPI84</t>
+          <t>https://www.youtube.com/shorts/lTSdbsVIKB4</t>
         </is>
       </c>
     </row>
@@ -7465,27 +7465,27 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>5 ChatGPT Secret Codes</t>
+          <t>Best website for students - don't miss</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+ChatGPT+Secret+Codes</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 ChatGPT Secret Codes</t>
+          <t>AI application featured in StudyTools: Best Website for Students - Don't Miss</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>5 ChatGPT Secret Codes</t>
+          <t>Best Website for Students - Don't Miss</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/KPRFyCuKvXs</t>
+          <t>https://www.youtube.com/shorts/W3tWNISZerA</t>
         </is>
       </c>
     </row>
@@ -7497,27 +7497,27 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>5 Gemini Secret Codes</t>
+          <t>Biggest problem of students</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Gemini+Secret+Codes</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Gemini Secret Codes</t>
+          <t>AI application featured in StudyTools: Biggest Problem of Students</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>5 Gemini Secret Codes</t>
+          <t>Biggest Problem of Students</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/k7JoNgbUduc</t>
+          <t>https://www.youtube.com/shorts/A0n2hsiXtP8</t>
         </is>
       </c>
     </row>
@@ -7529,27 +7529,27 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>5 Sector AI for Students</t>
+          <t>Chatgpt 3 secret &amp; important codes</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=5+Sector+AI+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 5 Sector AI for Students</t>
+          <t>AI application featured in StudyTools: ChatGPT 3 Secret &amp; Important Codes</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>5 Sector AI for Students</t>
+          <t>ChatGPT 3 Secret &amp; Important Codes</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/rXr861XdpCc</t>
+          <t>https://www.youtube.com/shorts/AZ2k8mV8ygo</t>
         </is>
       </c>
     </row>
@@ -7561,27 +7561,27 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>6 Secret AI tools for Students</t>
+          <t>Chatgpt 3 secret codes</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=6+Secret+AI+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 6 Secret AI tools for Students</t>
+          <t>AI application featured in StudyTools: ChatGPT 3 Secret Codes</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>6 Secret AI tools for Students</t>
+          <t>ChatGPT 3 Secret Codes</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/OtJwWNu2k4o</t>
+          <t>https://www.youtube.com/shorts/exGo6kMh-gc</t>
         </is>
       </c>
     </row>
@@ -7593,27 +7593,27 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>7 Secret Websites for Students</t>
+          <t>Chatgpt 5 secret codes</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=7+Secret+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 7 Secret Websites for Students</t>
+          <t>AI application featured in StudyTools: ChatGPT 5 Secret Codes</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>7 Secret Websites for Students</t>
+          <t>ChatGPT 5 Secret Codes</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/I0V0V-JuUyA</t>
+          <t>https://www.youtube.com/shorts/7wKB6oVGt5A</t>
         </is>
       </c>
     </row>
@@ -7625,27 +7625,27 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>7 Useful Ai tools for Students</t>
+          <t>Colourful notes free</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=7+Useful+Ai+tools+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 7 Useful Ai tools for Students</t>
+          <t>AI application featured in StudyTools: Make Colourful Notes Free</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>7 Useful Ai tools for Students</t>
+          <t>Make Colourful Notes Free</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/BVNLM_LAzL4</t>
+          <t>https://www.youtube.com/shorts/ZO0DgJqFoUs</t>
         </is>
       </c>
     </row>
@@ -7657,27 +7657,27 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>7 Useful Websites for Students</t>
+          <t>Convert study notes into song</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=7+Useful+Websites+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 7 Useful Websites for Students</t>
+          <t>AI application featured in StudyTools: Convert Study Notes into Song</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>7 Useful Websites for Students</t>
+          <t>Convert Study Notes into Song</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/fdkf0alHgbE</t>
+          <t>https://www.youtube.com/shorts/S44qjWGB_hQ</t>
         </is>
       </c>
     </row>
@@ -7689,27 +7689,27 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>90% Students Don't Know ?</t>
+          <t>Google 5 free ai courses</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=90+Students+Dont+Know</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 90% Students Don't Know ?</t>
+          <t>AI application featured in StudyTools: Google 5 Free AI Courses</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>90% Students Don't Know ?</t>
+          <t>Google 5 Free AI Courses</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/fYnnTa33be0</t>
+          <t>https://www.youtube.com/shorts/DNm4-P0aXgU</t>
         </is>
       </c>
     </row>
@@ -7721,27 +7721,27 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>99% Students Don't Know</t>
+          <t>Handwritten notes banao free</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=99+Students+Dont+Know</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: 99% Students Don't Know</t>
+          <t>AI application featured in StudyTools: Handwritten Notes Banao Free</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>99% Students Don't Know</t>
+          <t>Handwritten Notes Banao Free</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/IHpUMVW47hA</t>
+          <t>https://www.youtube.com/shorts/H-mTDrFt6hA</t>
         </is>
       </c>
     </row>
@@ -7753,27 +7753,27 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Ai tool for Exam Preparation</t>
+          <t>Handwritten notes for free</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Ai+tool+for+Exam+Preparation</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Ai tool for Exam Preparation</t>
+          <t>AI application featured in StudyTools: Make Handwritten Notes for free</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Ai tool for Exam Preparation</t>
+          <t>Make Handwritten Notes for free</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/4j3sxkHTivY</t>
+          <t>https://www.youtube.com/shorts/QjB-G6E4a9o</t>
         </is>
       </c>
     </row>
@@ -7785,27 +7785,27 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Amazing &amp; Secret Ai tool</t>
+          <t>Hidden secret for students</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing++Secret+Ai+tool</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing &amp; Secret Ai tool</t>
+          <t>AI application featured in StudyTools: Hidden Secret for Students</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Amazing &amp; Secret Ai tool</t>
+          <t>Hidden Secret for Students</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/vsWCMWnopiI</t>
+          <t>https://www.youtube.com/shorts/oQ43HkvXNwI</t>
         </is>
       </c>
     </row>
@@ -7817,27 +7817,27 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Amazing Ai tool for Students</t>
+          <t>Hidden tricks for students</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+Ai+tool+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing Ai tool for Students</t>
+          <t>AI application featured in StudyTools: Hidden Tricks for Students</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Amazing Ai tool for Students</t>
+          <t>Hidden Tricks for Students</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/A_PkccGaNoc</t>
+          <t>https://www.youtube.com/shorts/v0iGG7ZV9Dc</t>
         </is>
       </c>
     </row>
@@ -7849,27 +7849,27 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Amazing Ai tool- Don't Miss</t>
+          <t>Recover deleted files windows 11</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+Ai+tool+Dont+Miss</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing Ai tool- Don't Miss</t>
+          <t>AI application featured in StudyTools: Recover Deleted Files Windows 11</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>Amazing Ai tool- Don't Miss</t>
+          <t>Recover Deleted Files Windows 11</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/rv4DX0UMYvo</t>
+          <t>https://www.youtube.com/shorts/0jUuabSczls</t>
         </is>
       </c>
     </row>
@@ -7881,27 +7881,27 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Amazing Trick for Students</t>
+          <t>Secret &amp; amazing ai tool for smart study</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+Trick+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing Trick for Students</t>
+          <t>AI application featured in StudyTools: Secret &amp; Amazing Ai tool for Smart Study</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Amazing Trick for Students</t>
+          <t>Secret &amp; Amazing Ai tool for Smart Study</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/tXPl1YWSf5o</t>
+          <t>https://www.youtube.com/shorts/iFnT26mIwag</t>
         </is>
       </c>
     </row>
@@ -7913,27 +7913,27 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Amazing Website for Students</t>
+          <t>Secret &amp; hidden ai tool for students</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Amazing+Website+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Amazing Website for Students</t>
+          <t>AI application featured in StudyTools: Secret &amp; Hidden Ai tool for Students</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>Amazing Website for Students</t>
+          <t>Secret &amp; Hidden Ai tool for Students</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/Cb0wsxJZGK4</t>
+          <t>https://www.youtube.com/shorts/WQiSKoQu_r4</t>
         </is>
       </c>
     </row>
@@ -7945,27 +7945,27 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Average Salary 25-30 Lacs</t>
+          <t>Secret ai for students</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Average+Salary+2530+Lacs</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Average Salary 25-30 Lacs</t>
+          <t>AI application featured in StudyTools: Secret AI for Students</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Average Salary 25-30 Lacs</t>
+          <t>Secret AI for Students</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/2O5ZSvgljCk</t>
+          <t>https://www.youtube.com/shorts/7Skzm58Jeqs</t>
         </is>
       </c>
     </row>
@@ -7977,27 +7977,27 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Best AI tool for Students</t>
+          <t>Secret ai tool - don't miss</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+AI+tool+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best AI tool for Students</t>
+          <t>AI application featured in StudyTools: Secret Ai tool - Don't Miss</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>Best AI tool for Students</t>
+          <t>Secret Ai tool - Don't Miss</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/RwiXc1YWloU</t>
+          <t>https://www.youtube.com/shorts/AswMoZiGias</t>
         </is>
       </c>
     </row>
@@ -8009,27 +8009,27 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Best Ai Tool for Students - Topper se aage</t>
+          <t>Secret ai tool- don't miss</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Ai+Tool+for+Students++Topper+se+aage</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Ai Tool for Students - Topper se aage</t>
+          <t>AI application featured in StudyTools: Secret Ai tool- Don't Miss</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Best Ai Tool for Students - Topper se aage</t>
+          <t>Secret Ai tool- Don't Miss</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/xvYTzAtCrZY</t>
+          <t>https://www.youtube.com/shorts/NKz_TKA_IbI</t>
         </is>
       </c>
     </row>
@@ -8041,27 +8041,27 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Best Ai app for Students</t>
+          <t>Secret for students - don't miss</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Ai+app+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Ai app for Students</t>
+          <t>AI application featured in StudyTools: Secret For Students - Don't Miss</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>Best Ai app for Students</t>
+          <t>Secret For Students - Don't Miss</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/ysnBWYnY_l8</t>
+          <t>https://www.youtube.com/shorts/dvQahNfmnx0</t>
         </is>
       </c>
     </row>
@@ -8073,27 +8073,27 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Best Ai hack for Students</t>
+          <t>Super useful website for students</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Ai+hack+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Ai hack for Students</t>
+          <t>AI application featured in StudyTools: Super Useful Website for Students</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Best Ai hack for Students</t>
+          <t>Super Useful Website for Students</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/-ybptTMGa2M</t>
+          <t>https://www.youtube.com/shorts/ufuk8MSoIdg</t>
         </is>
       </c>
     </row>
@@ -8105,27 +8105,27 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Best Secret app for Generating Profile Pictur</t>
+          <t>Toolify.ai</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Secret+app+for+Generating+Profile+Pictures</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Secret app for Generating Profile Pictures</t>
+          <t>The world's most comprehensive directory of new AI tools, apps, and software updated daily.</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>Best Secret app for Generating Profile Pictures</t>
+          <t>2 Best Ai tools for Students</t>
         </is>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/shorts/BwYnj6rWwao</t>
+          <t>https://www.youtube.com/shorts/0mWolQnd5kA</t>
         </is>
       </c>
     </row>
@@ -8137,825 +8137,25 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Students</t>
+          <t>Useful ai tool for students</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Students</t>
+          <t>https://toolify.ai</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Students</t>
+          <t>AI application featured in StudyTools: Useful Ai tool for Students</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Best Website for Students</t>
+          <t>Useful Ai tool for Students</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/lTSdbsVIKB4</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="22" customHeight="1">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>Best Website for Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="C241" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Best+Website+for+Students++Dont+Miss</t>
-        </is>
-      </c>
-      <c r="D241" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Best Website for Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="E241" s="4" t="inlineStr">
-        <is>
-          <t>Best Website for Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="F241" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/W3tWNISZerA</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="22" customHeight="1">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>Biggest Problem of Students</t>
-        </is>
-      </c>
-      <c r="C242" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Biggest+Problem+of+Students</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Biggest Problem of Students</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr">
-        <is>
-          <t>Biggest Problem of Students</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/A0n2hsiXtP8</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="22" customHeight="1">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT 3 Secret &amp; Important Codes</t>
-        </is>
-      </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=ChatGPT+3+Secret++Important+Codes</t>
-        </is>
-      </c>
-      <c r="D243" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: ChatGPT 3 Secret &amp; Important Codes</t>
-        </is>
-      </c>
-      <c r="E243" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT 3 Secret &amp; Important Codes</t>
-        </is>
-      </c>
-      <c r="F243" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/AZ2k8mV8ygo</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="22" customHeight="1">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>ChatGPT 3 Secret Codes</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=ChatGPT+3+Secret+Codes</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: ChatGPT 3 Secret Codes</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>ChatGPT 3 Secret Codes</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/exGo6kMh-gc</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="22" customHeight="1">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT 5 Secret Codes</t>
-        </is>
-      </c>
-      <c r="C245" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=ChatGPT+5+Secret+Codes</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: ChatGPT 5 Secret Codes</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT 5 Secret Codes</t>
-        </is>
-      </c>
-      <c r="F245" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/7wKB6oVGt5A</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="22" customHeight="1">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>Convert Study Notes into Song</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Convert+Study+Notes+into+Song</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Convert Study Notes into Song</t>
-        </is>
-      </c>
-      <c r="E246" s="2" t="inlineStr">
-        <is>
-          <t>Convert Study Notes into Song</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/S44qjWGB_hQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="22" customHeight="1">
-      <c r="A247" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B247" s="4" t="inlineStr">
-        <is>
-          <t>Google 5 Free AI Courses</t>
-        </is>
-      </c>
-      <c r="C247" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Google+5+Free+AI+Courses</t>
-        </is>
-      </c>
-      <c r="D247" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Google 5 Free AI Courses</t>
-        </is>
-      </c>
-      <c r="E247" s="4" t="inlineStr">
-        <is>
-          <t>Google 5 Free AI Courses</t>
-        </is>
-      </c>
-      <c r="F247" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/DNm4-P0aXgU</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="22" customHeight="1">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>Handwritten Notes Banao Free</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Handwritten+Notes+Banao+Free</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Handwritten Notes Banao Free</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="inlineStr">
-        <is>
-          <t>Handwritten Notes Banao Free</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/H-mTDrFt6hA</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="22" customHeight="1">
-      <c r="A249" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>Hidden Secret for Students</t>
-        </is>
-      </c>
-      <c r="C249" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Hidden+Secret+for+Students</t>
-        </is>
-      </c>
-      <c r="D249" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Hidden Secret for Students</t>
-        </is>
-      </c>
-      <c r="E249" s="4" t="inlineStr">
-        <is>
-          <t>Hidden Secret for Students</t>
-        </is>
-      </c>
-      <c r="F249" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/oQ43HkvXNwI</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="22" customHeight="1">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>Hidden Tricks for Students</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Hidden+Tricks+for+Students</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Hidden Tricks for Students</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="inlineStr">
-        <is>
-          <t>Hidden Tricks for Students</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/v0iGG7ZV9Dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="22" customHeight="1">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>Make Colourful Notes Free</t>
-        </is>
-      </c>
-      <c r="C251" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Make+Colourful+Notes+Free</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Make Colourful Notes Free</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="inlineStr">
-        <is>
-          <t>Make Colourful Notes Free</t>
-        </is>
-      </c>
-      <c r="F251" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/ZO0DgJqFoUs</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="22" customHeight="1">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>Make Handwritten Notes for free</t>
-        </is>
-      </c>
-      <c r="C252" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Make+Handwritten+Notes+for+free</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Make Handwritten Notes for free</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>Make Handwritten Notes for free</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/QjB-G6E4a9o</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="1">
-      <c r="A253" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B253" s="4" t="inlineStr">
-        <is>
-          <t>Recover Deleted Files Windows 11</t>
-        </is>
-      </c>
-      <c r="C253" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Recover+Deleted+Files+Windows+11</t>
-        </is>
-      </c>
-      <c r="D253" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Recover Deleted Files Windows 11</t>
-        </is>
-      </c>
-      <c r="E253" s="4" t="inlineStr">
-        <is>
-          <t>Recover Deleted Files Windows 11</t>
-        </is>
-      </c>
-      <c r="F253" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/0jUuabSczls</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="22" customHeight="1">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>Secret &amp; Amazing Ai tool for Smart Study</t>
-        </is>
-      </c>
-      <c r="C254" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret++Amazing+Ai+tool+for+Smart+Study</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret &amp; Amazing Ai tool for Smart Study</t>
-        </is>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>Secret &amp; Amazing Ai tool for Smart Study</t>
-        </is>
-      </c>
-      <c r="F254" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/iFnT26mIwag</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="22" customHeight="1">
-      <c r="A255" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B255" s="4" t="inlineStr">
-        <is>
-          <t>Secret &amp; Hidden Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="C255" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret++Hidden+Ai+tool+for+Students</t>
-        </is>
-      </c>
-      <c r="D255" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret &amp; Hidden Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="E255" s="4" t="inlineStr">
-        <is>
-          <t>Secret &amp; Hidden Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/WQiSKoQu_r4</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="22" customHeight="1">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>Secret AI for Students</t>
-        </is>
-      </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret+AI+for+Students</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret AI for Students</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>Secret AI for Students</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/7Skzm58Jeqs</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="22" customHeight="1">
-      <c r="A257" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>Secret AI tool for Students</t>
-        </is>
-      </c>
-      <c r="C257" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret+AI+tool+for+Students</t>
-        </is>
-      </c>
-      <c r="D257" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret AI tool for Students</t>
-        </is>
-      </c>
-      <c r="E257" s="4" t="inlineStr">
-        <is>
-          <t>Secret AI tool for Students</t>
-        </is>
-      </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/gt9hM8bnaGU</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="22" customHeight="1">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>Secret AI tool for Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret+AI+tool+for+Students++Dont+Miss</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret AI tool for Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>Secret AI tool for Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="F258" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/KD60Q1MFmWc</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="22" customHeight="1">
-      <c r="A259" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>Secret Ai tool - Don't Miss</t>
-        </is>
-      </c>
-      <c r="C259" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret+Ai+tool++Dont+Miss</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret Ai tool - Don't Miss</t>
-        </is>
-      </c>
-      <c r="E259" s="4" t="inlineStr">
-        <is>
-          <t>Secret Ai tool - Don't Miss</t>
-        </is>
-      </c>
-      <c r="F259" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/AswMoZiGias</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="22" customHeight="1">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>Secret Ai tool- Don't Miss</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret+Ai+tool+Dont+Miss</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret Ai tool- Don't Miss</t>
-        </is>
-      </c>
-      <c r="E260" s="2" t="inlineStr">
-        <is>
-          <t>Secret Ai tool- Don't Miss</t>
-        </is>
-      </c>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/NKz_TKA_IbI</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="22" customHeight="1">
-      <c r="A261" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>Secret For Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret+For+Students++Dont+Miss</t>
-        </is>
-      </c>
-      <c r="D261" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret For Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="E261" s="4" t="inlineStr">
-        <is>
-          <t>Secret For Students - Don't Miss</t>
-        </is>
-      </c>
-      <c r="F261" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/dvQahNfmnx0</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="22" customHeight="1">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>Secret ai tool for Students - Try Now</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Secret+ai+tool+for+Students++Try+Now</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Secret ai tool for Students - Try Now</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>Secret ai tool for Students - Try Now</t>
-        </is>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/ngMcpsXEvAc</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="22" customHeight="1">
-      <c r="A263" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>Super Secret Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="C263" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Super+Secret+Ai+tool+for+Students</t>
-        </is>
-      </c>
-      <c r="D263" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Super Secret Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="E263" s="4" t="inlineStr">
-        <is>
-          <t>Super Secret Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="F263" s="5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/f7REGf2J4FU</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="22" customHeight="1">
-      <c r="A264" s="2" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>Super Useful Website for Students</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Super+Useful+Website+for+Students</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Super Useful Website for Students</t>
-        </is>
-      </c>
-      <c r="E264" s="2" t="inlineStr">
-        <is>
-          <t>Super Useful Website for Students</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/shorts/ufuk8MSoIdg</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="22" customHeight="1">
-      <c r="A265" s="4" t="inlineStr">
-        <is>
-          <t>🤖 AI &amp; Machine Learning Tools</t>
-        </is>
-      </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>Useful Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="C265" s="5" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Useful+Ai+tool+for+Students</t>
-        </is>
-      </c>
-      <c r="D265" s="4" t="inlineStr">
-        <is>
-          <t>Featured web tool in StudyTools showcase: Useful Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="E265" s="4" t="inlineStr">
-        <is>
-          <t>Useful Ai tool for Students</t>
-        </is>
-      </c>
-      <c r="F265" s="5" t="inlineStr">
         <is>
           <t>https://www.youtube.com/shorts/Qq5Hv4MhPYU</t>
         </is>
@@ -9441,56 +8641,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId476"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId477"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F251" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F252" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F253" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F254" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F255" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F256" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F257" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F258" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId528"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
